--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802106</v>
+        <v>127802487</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,14 +950,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481280</v>
+        <v>481325</v>
       </c>
       <c r="R4" t="n">
-        <v>6791734</v>
+        <v>6791701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +992,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127802239</v>
+        <v>127802106</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481187</v>
+        <v>481280</v>
       </c>
       <c r="R5" t="n">
-        <v>6791714</v>
+        <v>6791734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,11 +1098,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en brändstubbe</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127794232</v>
+        <v>127802239</v>
       </c>
       <c r="B6" t="n">
-        <v>79052</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,37 +1134,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481340</v>
+        <v>481187</v>
       </c>
       <c r="R6" t="n">
-        <v>6791650</v>
+        <v>6791714</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,19 +1194,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en brändstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,28 +1210,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127794033</v>
+        <v>127794232</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>79052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,43 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481385</v>
+        <v>481340</v>
       </c>
       <c r="R7" t="n">
-        <v>6791690</v>
+        <v>6791650</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1309,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127802487</v>
+        <v>127794033</v>
       </c>
       <c r="B8" t="n">
-        <v>79052</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,40 +1347,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481325</v>
+        <v>481385</v>
       </c>
       <c r="R8" t="n">
-        <v>6791701</v>
+        <v>6791690</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,14 +1413,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,64 +1434,68 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127795300</v>
+        <v>127794366</v>
       </c>
       <c r="B9" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481286</v>
+        <v>481336</v>
       </c>
       <c r="R9" t="n">
-        <v>6791603</v>
+        <v>6791622</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127801964</v>
+        <v>127795300</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>92628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,46 +1575,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481215</v>
+        <v>481286</v>
       </c>
       <c r="R10" t="n">
-        <v>6791716</v>
+        <v>6791603</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,18 +1632,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1659,7 +1664,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1778,53 +1783,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127794366</v>
+        <v>127801964</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481336</v>
+        <v>481215</v>
       </c>
       <c r="R12" t="n">
-        <v>6791622</v>
+        <v>6791716</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,27 +1860,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,60 +1883,58 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127794426</v>
+        <v>127801929</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>79052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481318</v>
+        <v>481193</v>
       </c>
       <c r="R13" t="n">
-        <v>6791597</v>
+        <v>6791718</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,32 +1961,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2000,17 +1984,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127794298</v>
+        <v>127802539</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,37 +2002,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481340</v>
+        <v>481318</v>
       </c>
       <c r="R14" t="n">
-        <v>6791650</v>
+        <v>6791660</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2075,19 +2062,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,71 +2078,70 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127795085</v>
+        <v>127802005</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481240</v>
+        <v>481219</v>
       </c>
       <c r="R15" t="n">
-        <v>6791516</v>
+        <v>6791708</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2187,27 +2168,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,17 +2191,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127801929</v>
+        <v>127794298</v>
       </c>
       <c r="B16" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,40 +2209,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481193</v>
+        <v>481340</v>
       </c>
       <c r="R16" t="n">
-        <v>6791718</v>
+        <v>6791650</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2297,18 +2266,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2320,58 +2298,60 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127802005</v>
+        <v>127795085</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481219</v>
+        <v>481240</v>
       </c>
       <c r="R17" t="n">
-        <v>6791708</v>
+        <v>6791516</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,18 +2378,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2421,14 +2410,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127793635</v>
+        <v>127802463</v>
       </c>
       <c r="B18" t="n">
         <v>57663</v>
@@ -2457,24 +2446,27 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481357</v>
+        <v>481355</v>
       </c>
       <c r="R18" t="n">
-        <v>6791712</v>
+        <v>6791722</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2501,19 +2493,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,12 +2515,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2647,56 +2634,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127802463</v>
+        <v>127794426</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481355</v>
+        <v>481318</v>
       </c>
       <c r="R20" t="n">
-        <v>6791722</v>
+        <v>6791597</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2723,14 +2707,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre hackmärken i gran</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,22 +2739,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127802539</v>
+        <v>127793635</v>
       </c>
       <c r="B21" t="n">
-        <v>79052</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,40 +2762,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481318</v>
+        <v>481357</v>
       </c>
       <c r="R21" t="n">
-        <v>6791660</v>
+        <v>6791712</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2828,14 +2824,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,69 +2845,63 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127794064</v>
+        <v>127793514</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>91303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481385</v>
+        <v>481353</v>
       </c>
       <c r="R22" t="n">
-        <v>6791690</v>
+        <v>6791723</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2975,45 +2970,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127793514</v>
+        <v>127794064</v>
       </c>
       <c r="B23" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481353</v>
+        <v>481385</v>
       </c>
       <c r="R23" t="n">
-        <v>6791723</v>
+        <v>6791690</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3082,50 +3082,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127793434</v>
+        <v>127794379</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481316</v>
+        <v>481338</v>
       </c>
       <c r="R24" t="n">
-        <v>6791716</v>
+        <v>6791608</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3157,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3167,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,7 +3295,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127795114</v>
+        <v>127793434</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3331,7 +3326,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3340,10 +3335,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481235</v>
+        <v>481316</v>
       </c>
       <c r="R26" t="n">
-        <v>6791533</v>
+        <v>6791716</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3375,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,45 +3407,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127794379</v>
+        <v>127795114</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481338</v>
+        <v>481235</v>
       </c>
       <c r="R27" t="n">
-        <v>6791608</v>
+        <v>6791533</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,60 +3512,58 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127794470</v>
+        <v>127801926</v>
       </c>
       <c r="B28" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481322</v>
+        <v>481193</v>
       </c>
       <c r="R28" t="n">
-        <v>6791606</v>
+        <v>6791718</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3592,32 +3590,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3629,14 +3613,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127801926</v>
+        <v>127802054</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3674,10 +3658,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481193</v>
+        <v>481267</v>
       </c>
       <c r="R29" t="n">
-        <v>6791718</v>
+        <v>6791723</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3737,51 +3721,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127802054</v>
+        <v>127794470</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481267</v>
+        <v>481322</v>
       </c>
       <c r="R30" t="n">
-        <v>6791723</v>
+        <v>6791606</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3808,18 +3794,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127801947</v>
+        <v>127802179</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,21 +3961,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,14 +3984,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481204</v>
+        <v>481186</v>
       </c>
       <c r="R32" t="n">
-        <v>6791711</v>
+        <v>6791726</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4026,6 +4026,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4039,22 +4044,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127802179</v>
+        <v>127801947</v>
       </c>
       <c r="B33" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4062,21 +4067,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,14 +4090,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481186</v>
+        <v>481204</v>
       </c>
       <c r="R33" t="n">
-        <v>6791726</v>
+        <v>6791711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,11 +4132,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4145,19 +4145,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127802354</v>
+        <v>127802625</v>
       </c>
       <c r="B34" t="n">
         <v>79052</v>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481294</v>
+        <v>481275</v>
       </c>
       <c r="R34" t="n">
-        <v>6791733</v>
+        <v>6791557</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4263,7 +4263,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802625</v>
+        <v>127802354</v>
       </c>
       <c r="B35" t="n">
         <v>79052</v>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481275</v>
+        <v>481294</v>
       </c>
       <c r="R35" t="n">
-        <v>6791557</v>
+        <v>6791733</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4575,17 +4575,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127794182</v>
+        <v>127802041</v>
       </c>
       <c r="B38" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,46 +4593,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481374</v>
+        <v>481251</v>
       </c>
       <c r="R38" t="n">
-        <v>6791645</v>
+        <v>6791716</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4659,27 +4653,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4691,60 +4676,64 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127794339</v>
+        <v>127802504</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481340</v>
+        <v>481325</v>
       </c>
       <c r="R39" t="n">
-        <v>6791650</v>
+        <v>6791701</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4771,49 +4760,40 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127802041</v>
+        <v>127794339</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,40 +4801,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481251</v>
+        <v>481340</v>
       </c>
       <c r="R40" t="n">
-        <v>6791716</v>
+        <v>6791650</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4881,18 +4863,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4904,64 +4895,64 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127802504</v>
+        <v>127794182</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481325</v>
+        <v>481374</v>
       </c>
       <c r="R41" t="n">
-        <v>6791701</v>
+        <v>6791645</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4988,30 +4979,39 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5333,53 +5333,51 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127793574</v>
+        <v>127802418</v>
       </c>
       <c r="B45" t="n">
-        <v>5177</v>
+        <v>79609</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481353</v>
+        <v>481333</v>
       </c>
       <c r="R45" t="n">
-        <v>6791723</v>
+        <v>6791733</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,19 +5404,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,69 +5420,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127802418</v>
+        <v>127793574</v>
       </c>
       <c r="B46" t="n">
-        <v>79609</v>
+        <v>5177</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481333</v>
+        <v>481353</v>
       </c>
       <c r="R46" t="n">
-        <v>6791733</v>
+        <v>6791723</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5516,14 +5512,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5532,29 +5533,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127792736</v>
+        <v>127802578</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5562,37 +5562,40 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481195</v>
+        <v>481315</v>
       </c>
       <c r="R47" t="n">
-        <v>6791715</v>
+        <v>6791571</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5619,19 +5622,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:42</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5640,18 +5638,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5860,10 +5859,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127802578</v>
+        <v>127792736</v>
       </c>
       <c r="B50" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5871,40 +5870,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481315</v>
+        <v>481195</v>
       </c>
       <c r="R50" t="n">
-        <v>6791571</v>
+        <v>6791715</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5931,14 +5927,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5947,19 +5948,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127796163</v>
+        <v>127802564</v>
       </c>
       <c r="B55" t="n">
-        <v>57823</v>
+        <v>79052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,42 +6409,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481305</v>
+        <v>481366</v>
       </c>
       <c r="R55" t="n">
-        <v>6791432</v>
+        <v>6791657</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6471,19 +6469,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6492,18 +6485,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6611,10 +6605,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127802564</v>
+        <v>127796163</v>
       </c>
       <c r="B57" t="n">
-        <v>79052</v>
+        <v>57823</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6622,40 +6616,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481366</v>
+        <v>481305</v>
       </c>
       <c r="R57" t="n">
-        <v>6791657</v>
+        <v>6791432</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6682,14 +6678,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6698,29 +6699,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127793176</v>
+        <v>127802522</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6728,37 +6728,40 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481316</v>
+        <v>481351</v>
       </c>
       <c r="R58" t="n">
-        <v>6791716</v>
+        <v>6791706</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6785,19 +6788,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:04</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6806,28 +6804,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127802522</v>
+        <v>127793176</v>
       </c>
       <c r="B59" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6835,40 +6834,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481351</v>
+        <v>481316</v>
       </c>
       <c r="R59" t="n">
-        <v>6791706</v>
+        <v>6791716</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6895,14 +6891,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6911,19 +6912,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7141,7 +7141,7 @@
         <v>127801935</v>
       </c>
       <c r="B62" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7451,17 +7451,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127802615</v>
+        <v>127801912</v>
       </c>
       <c r="B65" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,14 +7492,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481276</v>
+        <v>481175</v>
       </c>
       <c r="R65" t="n">
-        <v>6791608</v>
+        <v>6791725</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,11 +7534,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7552,22 +7547,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127801912</v>
+        <v>127802299</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7575,21 +7570,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7598,14 +7593,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481175</v>
+        <v>481213</v>
       </c>
       <c r="R66" t="n">
-        <v>6791725</v>
+        <v>6791709</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7640,6 +7635,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7653,19 +7653,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127802299</v>
+        <v>127802615</v>
       </c>
       <c r="B67" t="n">
         <v>79052</v>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481213</v>
+        <v>481276</v>
       </c>
       <c r="R67" t="n">
-        <v>6791709</v>
+        <v>6791608</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7768,6 +7768,577 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127794665</v>
+      </c>
+      <c r="B68" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>481309</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6791590</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ett par exemplar av spelspillning syns på stenen. Det som ytterligare talar för spel på denna plats är att stenen är sliten och avskavd på lavar och mossor. Stenen är belägen på en höjd nära en myr. Intill platsen med spelspillning hittades stjärtpenna av tupp, tuppdun vid balgrop samt även ytterligare en fjäder av tupp samt bajs. Sannolikt är det ett tjäderspel på båda sidor av myren, men detta behöver utredas ytterligare.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127835551</v>
+      </c>
+      <c r="B69" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>481194</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6791696</v>
+      </c>
+      <c r="S69" t="n">
+        <v>9</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127837613</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58098</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>481203</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6791678</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127836058</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78779</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>481222</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6791673</v>
+      </c>
+      <c r="S71" t="n">
+        <v>9</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127837582</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57549</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100100</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Bivråk</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pernis apivorus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>481203</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6791678</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -675,56 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127802601</v>
+        <v>127795277</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>56858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481305</v>
+        <v>481286</v>
       </c>
       <c r="R2" t="n">
-        <v>6791545</v>
+        <v>6791603</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,14 +762,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Stjärtfjäder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,79 +794,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127795277</v>
+        <v>127802601</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481286</v>
+        <v>481305</v>
       </c>
       <c r="R3" t="n">
-        <v>6791603</v>
+        <v>6791545</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,24 +882,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stjärtfjäder</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802487</v>
+        <v>127802239</v>
       </c>
       <c r="B4" t="n">
-        <v>79052</v>
+        <v>78782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481325</v>
+        <v>481187</v>
       </c>
       <c r="R4" t="n">
-        <v>6791701</v>
+        <v>6791714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en brändstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127802106</v>
+        <v>127794232</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,40 +1033,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481280</v>
+        <v>481340</v>
       </c>
       <c r="R5" t="n">
-        <v>6791734</v>
+        <v>6791650</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,18 +1090,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,17 +1122,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127802239</v>
+        <v>127794033</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,40 +1140,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481187</v>
+        <v>481385</v>
       </c>
       <c r="R6" t="n">
-        <v>6791714</v>
+        <v>6791690</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,14 +1206,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en brändstubbe</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,29 +1227,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127794232</v>
+        <v>127802487</v>
       </c>
       <c r="B7" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,19 +1274,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481340</v>
+        <v>481325</v>
       </c>
       <c r="R7" t="n">
-        <v>6791650</v>
+        <v>6791701</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,19 +1316,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,28 +1332,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127794033</v>
+        <v>127802106</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,46 +1362,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481385</v>
+        <v>481280</v>
       </c>
       <c r="R8" t="n">
-        <v>6791690</v>
+        <v>6791734</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,27 +1422,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,60 +1445,64 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127794366</v>
+        <v>127801964</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481336</v>
+        <v>481215</v>
       </c>
       <c r="R9" t="n">
-        <v>6791622</v>
+        <v>6791716</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,27 +1529,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1567,7 +1562,7 @@
         <v>127795300</v>
       </c>
       <c r="B10" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,38 +1666,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794623</v>
+        <v>127794366</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1711,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481309</v>
+        <v>481336</v>
       </c>
       <c r="R11" t="n">
-        <v>6791590</v>
+        <v>6791622</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1746,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,7 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,7 +1778,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127801964</v>
+        <v>127794623</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1812,28 +1807,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481215</v>
+        <v>481309</v>
       </c>
       <c r="R12" t="n">
-        <v>6791716</v>
+        <v>6791590</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,18 +1851,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127801929</v>
+        <v>127793859</v>
       </c>
       <c r="B13" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,22 +1919,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481193</v>
+        <v>481377</v>
       </c>
       <c r="R13" t="n">
-        <v>6791718</v>
+        <v>6791659</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,18 +1958,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,58 +1990,60 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127802539</v>
+        <v>127794426</v>
       </c>
       <c r="B14" t="n">
-        <v>79052</v>
+        <v>56858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>481318</v>
       </c>
       <c r="R14" t="n">
-        <v>6791660</v>
+        <v>6791597</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,14 +2070,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,70 +2096,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127802005</v>
+        <v>127795085</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481219</v>
+        <v>481240</v>
       </c>
       <c r="R15" t="n">
-        <v>6791708</v>
+        <v>6791516</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2168,18 +2187,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2191,17 +2219,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127794298</v>
+        <v>127802005</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,19 +2255,22 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481340</v>
+        <v>481219</v>
       </c>
       <c r="R16" t="n">
-        <v>6791650</v>
+        <v>6791708</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,27 +2297,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2298,57 +2320,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127795085</v>
+        <v>127794298</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481240</v>
+        <v>481340</v>
       </c>
       <c r="R17" t="n">
-        <v>6791516</v>
+        <v>6791650</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2397,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2407,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2434,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127802463</v>
+        <v>127793635</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,27 +2463,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481355</v>
+        <v>481357</v>
       </c>
       <c r="R18" t="n">
-        <v>6791722</v>
+        <v>6791712</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2493,14 +2507,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken i gran</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2515,22 +2534,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127793859</v>
+        <v>127801929</v>
       </c>
       <c r="B19" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,19 +2575,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481377</v>
+        <v>481193</v>
       </c>
       <c r="R19" t="n">
-        <v>6791659</v>
+        <v>6791718</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2595,27 +2617,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2627,60 +2640,58 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127794426</v>
+        <v>127802539</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>79055</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>481318</v>
       </c>
       <c r="R20" t="n">
-        <v>6791597</v>
+        <v>6791660</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2707,24 +2718,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2733,28 +2734,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127793635</v>
+        <v>127802463</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,24 +2782,27 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481357</v>
+        <v>481355</v>
       </c>
       <c r="R21" t="n">
-        <v>6791712</v>
+        <v>6791722</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2824,19 +2829,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,12 +2851,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
         <v>127793514</v>
       </c>
       <c r="B22" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>127794064</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,45 +3082,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127794379</v>
+        <v>127793434</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481338</v>
+        <v>481316</v>
       </c>
       <c r="R24" t="n">
-        <v>6791608</v>
+        <v>6791716</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3152,7 +3157,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3167,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,51 +3194,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127802326</v>
+        <v>127795114</v>
       </c>
       <c r="B25" t="n">
-        <v>79052</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481261</v>
+        <v>481235</v>
       </c>
       <c r="R25" t="n">
-        <v>6791722</v>
+        <v>6791533</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3260,14 +3267,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,69 +3288,63 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127793434</v>
+        <v>127794379</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481316</v>
+        <v>481338</v>
       </c>
       <c r="R26" t="n">
-        <v>6791716</v>
+        <v>6791608</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3370,7 +3376,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3386,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,53 +3413,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127795114</v>
+        <v>127802326</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481235</v>
+        <v>481261</v>
       </c>
       <c r="R27" t="n">
-        <v>6791533</v>
+        <v>6791722</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3480,19 +3484,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,69 +3500,72 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127801926</v>
+        <v>127794470</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>56858</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R28" t="n">
-        <v>6791718</v>
+        <v>6791606</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,18 +3592,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3613,58 +3629,60 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127802054</v>
+        <v>127794518</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481267</v>
+        <v>481322</v>
       </c>
       <c r="R29" t="n">
-        <v>6791723</v>
+        <v>6791606</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3691,18 +3709,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3714,60 +3741,58 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127794470</v>
+        <v>127801926</v>
       </c>
       <c r="B30" t="n">
-        <v>56855</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481322</v>
+        <v>481193</v>
       </c>
       <c r="R30" t="n">
-        <v>6791606</v>
+        <v>6791718</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3794,32 +3819,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3831,60 +3842,58 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127794518</v>
+        <v>127802054</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481322</v>
+        <v>481267</v>
       </c>
       <c r="R31" t="n">
-        <v>6791606</v>
+        <v>6791723</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3911,27 +3920,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3953,7 +3953,7 @@
         <v>127802179</v>
       </c>
       <c r="B32" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>127801947</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>127802625</v>
       </c>
       <c r="B34" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>127802354</v>
       </c>
       <c r="B35" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127802650</v>
       </c>
       <c r="B36" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>127794572</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4575,17 +4575,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127802041</v>
+        <v>127794339</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,40 +4593,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481251</v>
+        <v>481340</v>
       </c>
       <c r="R38" t="n">
-        <v>6791716</v>
+        <v>6791650</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4653,18 +4655,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4676,64 +4687,64 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127802504</v>
+        <v>127794182</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481325</v>
+        <v>481374</v>
       </c>
       <c r="R39" t="n">
-        <v>6791701</v>
+        <v>6791645</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4760,83 +4771,96 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127794339</v>
+        <v>127802504</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481340</v>
+        <v>481325</v>
       </c>
       <c r="R40" t="n">
-        <v>6791650</v>
+        <v>6791701</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4863,49 +4887,40 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127794182</v>
+        <v>127802041</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4913,46 +4928,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481374</v>
+        <v>481251</v>
       </c>
       <c r="R41" t="n">
-        <v>6791645</v>
+        <v>6791716</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4979,27 +4988,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5011,17 +5011,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127802033</v>
+        <v>127795149</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5047,22 +5047,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481244</v>
+        <v>481247</v>
       </c>
       <c r="R42" t="n">
-        <v>6791710</v>
+        <v>6791558</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5089,18 +5086,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5112,17 +5118,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127795149</v>
+        <v>127795235</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5154,10 +5160,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481247</v>
+        <v>481286</v>
       </c>
       <c r="R43" t="n">
-        <v>6791558</v>
+        <v>6791603</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5189,7 +5195,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5205,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,17 +5225,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127795235</v>
+        <v>127802033</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5255,19 +5261,22 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481286</v>
+        <v>481244</v>
       </c>
       <c r="R44" t="n">
-        <v>6791603</v>
+        <v>6791710</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5294,27 +5303,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5326,58 +5326,60 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127802418</v>
+        <v>127793574</v>
       </c>
       <c r="B45" t="n">
-        <v>79609</v>
+        <v>5177</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481333</v>
+        <v>481353</v>
       </c>
       <c r="R45" t="n">
-        <v>6791733</v>
+        <v>6791723</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5404,14 +5406,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5420,72 +5427,69 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127793574</v>
+        <v>127802418</v>
       </c>
       <c r="B46" t="n">
-        <v>5177</v>
+        <v>79612</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481353</v>
+        <v>481333</v>
       </c>
       <c r="R46" t="n">
-        <v>6791723</v>
+        <v>6791733</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5512,19 +5516,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5533,28 +5532,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127802578</v>
+        <v>127792736</v>
       </c>
       <c r="B47" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5562,40 +5562,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481315</v>
+        <v>481195</v>
       </c>
       <c r="R47" t="n">
-        <v>6791571</v>
+        <v>6791715</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5622,14 +5619,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5638,70 +5640,71 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127801956</v>
+        <v>127794070</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481214</v>
+        <v>481378</v>
       </c>
       <c r="R48" t="n">
-        <v>6791711</v>
+        <v>6791650</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5728,18 +5731,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5751,17 +5763,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127802109</v>
+        <v>127802578</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,21 +5781,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5792,14 +5804,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481301</v>
+        <v>481315</v>
       </c>
       <c r="R49" t="n">
-        <v>6791736</v>
+        <v>6791571</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,6 +5846,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5847,22 +5864,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127792736</v>
+        <v>127801956</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5888,19 +5905,22 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481195</v>
+        <v>481214</v>
       </c>
       <c r="R50" t="n">
-        <v>6791715</v>
+        <v>6791711</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5927,27 +5947,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5959,60 +5970,58 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127794070</v>
+        <v>127802109</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481378</v>
+        <v>481301</v>
       </c>
       <c r="R51" t="n">
-        <v>6791650</v>
+        <v>6791736</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6039,27 +6048,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6081,7 +6081,7 @@
         <v>127802018</v>
       </c>
       <c r="B52" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>127793494</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>127793626</v>
       </c>
       <c r="B54" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>127802564</v>
       </c>
       <c r="B55" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>127802064</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>127796163</v>
       </c>
       <c r="B57" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127802522</v>
+        <v>127793176</v>
       </c>
       <c r="B58" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6728,40 +6728,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481351</v>
+        <v>481316</v>
       </c>
       <c r="R58" t="n">
-        <v>6791706</v>
+        <v>6791716</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6788,14 +6785,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6804,29 +6806,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127793176</v>
+        <v>127802522</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6834,37 +6835,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481316</v>
+        <v>481351</v>
       </c>
       <c r="R59" t="n">
-        <v>6791716</v>
+        <v>6791706</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6891,19 +6895,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:04</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,18 +6911,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6933,7 +6933,7 @@
         <v>127793847</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>127802028</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>127801935</v>
       </c>
       <c r="B62" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127793724</v>
+        <v>127794591</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>79055</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7250,39 +7250,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481344</v>
+        <v>481322</v>
       </c>
       <c r="R63" t="n">
-        <v>6791702</v>
+        <v>6791606</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7314,7 +7309,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7324,7 +7319,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7344,17 +7339,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127794591</v>
+        <v>127793724</v>
       </c>
       <c r="B64" t="n">
-        <v>79052</v>
+        <v>57666</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,34 +7357,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481322</v>
+        <v>481344</v>
       </c>
       <c r="R64" t="n">
-        <v>6791606</v>
+        <v>6791702</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7451,17 +7451,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127801912</v>
+        <v>127802299</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,14 +7492,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481175</v>
+        <v>481213</v>
       </c>
       <c r="R65" t="n">
-        <v>6791725</v>
+        <v>6791709</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,6 +7534,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7547,22 +7552,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127802299</v>
+        <v>127802615</v>
       </c>
       <c r="B66" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7597,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481213</v>
+        <v>481276</v>
       </c>
       <c r="R66" t="n">
-        <v>6791709</v>
+        <v>6791608</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7665,10 +7670,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127802615</v>
+        <v>127801912</v>
       </c>
       <c r="B67" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7676,21 +7681,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7699,14 +7704,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481276</v>
+        <v>481175</v>
       </c>
       <c r="R67" t="n">
-        <v>6791608</v>
+        <v>6791725</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,11 +7746,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,12 +7759,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7774,7 +7774,7 @@
         <v>127794665</v>
       </c>
       <c r="B68" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>127835551</v>
       </c>
       <c r="B69" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>127837613</v>
       </c>
       <c r="B70" t="n">
-        <v>58098</v>
+        <v>58101</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>127836058</v>
       </c>
       <c r="B71" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>127837582</v>
       </c>
       <c r="B72" t="n">
-        <v>57549</v>
+        <v>57552</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127795277</v>
       </c>
       <c r="B2" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>127802601</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802239</v>
+        <v>127794232</v>
       </c>
       <c r="B4" t="n">
-        <v>78782</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,40 +927,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481187</v>
+        <v>481340</v>
       </c>
       <c r="R4" t="n">
-        <v>6791714</v>
+        <v>6791650</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,14 +984,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en brändstubbe</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,29 +1005,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127794232</v>
+        <v>127794033</v>
       </c>
       <c r="B5" t="n">
-        <v>79055</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,34 +1034,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481340</v>
+        <v>481385</v>
       </c>
       <c r="R5" t="n">
-        <v>6791650</v>
+        <v>6791690</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1092,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127794033</v>
+        <v>127802106</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,46 +1150,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481385</v>
+        <v>481280</v>
       </c>
       <c r="R6" t="n">
-        <v>6791690</v>
+        <v>6791734</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,27 +1210,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,7 +1233,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1248,7 +1243,7 @@
         <v>127802487</v>
       </c>
       <c r="B7" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127802106</v>
+        <v>127802239</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1385,14 +1380,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481280</v>
+        <v>481187</v>
       </c>
       <c r="R8" t="n">
-        <v>6791734</v>
+        <v>6791714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,6 +1422,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en brändstubbe</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1440,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127801964</v>
+        <v>127795300</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>92639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,46 +1463,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481215</v>
+        <v>481286</v>
       </c>
       <c r="R9" t="n">
-        <v>6791716</v>
+        <v>6791603</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,18 +1520,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1552,52 +1552,57 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127795300</v>
+        <v>127794366</v>
       </c>
       <c r="B10" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481286</v>
+        <v>481336</v>
       </c>
       <c r="R10" t="n">
-        <v>6791603</v>
+        <v>6791622</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1629,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1639,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,45 +1664,45 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794366</v>
+        <v>127794623</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1706,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481336</v>
+        <v>481309</v>
       </c>
       <c r="R11" t="n">
-        <v>6791622</v>
+        <v>6791590</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1741,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1756,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,7 +1783,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127794623</v>
+        <v>127801964</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1807,24 +1812,28 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481309</v>
+        <v>481215</v>
       </c>
       <c r="R12" t="n">
-        <v>6791590</v>
+        <v>6791716</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,27 +1860,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127793859</v>
+        <v>127794298</v>
       </c>
       <c r="B13" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481377</v>
+        <v>481340</v>
       </c>
       <c r="R13" t="n">
-        <v>6791659</v>
+        <v>6791650</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,45 +1990,45 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127794426</v>
+        <v>127793635</v>
       </c>
       <c r="B14" t="n">
-        <v>56858</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481318</v>
+        <v>481357</v>
       </c>
       <c r="R14" t="n">
-        <v>6791597</v>
+        <v>6791712</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2082,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,53 +2109,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127795085</v>
+        <v>127801929</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481240</v>
+        <v>481193</v>
       </c>
       <c r="R15" t="n">
-        <v>6791516</v>
+        <v>6791718</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2187,27 +2180,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,7 +2203,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2229,7 +2213,7 @@
         <v>127802005</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127794298</v>
+        <v>127802463</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,37 +2322,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481340</v>
+        <v>481355</v>
       </c>
       <c r="R17" t="n">
-        <v>6791650</v>
+        <v>6791722</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2395,19 +2387,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,22 +2409,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127793635</v>
+        <v>127793859</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>79061</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,39 +2432,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481357</v>
+        <v>481377</v>
       </c>
       <c r="R18" t="n">
-        <v>6791712</v>
+        <v>6791659</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2546,51 +2528,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127801929</v>
+        <v>127794426</v>
       </c>
       <c r="B19" t="n">
-        <v>79055</v>
+        <v>56864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481193</v>
+        <v>481318</v>
       </c>
       <c r="R19" t="n">
-        <v>6791718</v>
+        <v>6791597</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,18 +2601,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2640,58 +2638,60 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127802539</v>
+        <v>127795085</v>
       </c>
       <c r="B20" t="n">
-        <v>79055</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481318</v>
+        <v>481240</v>
       </c>
       <c r="R20" t="n">
-        <v>6791660</v>
+        <v>6791516</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2718,14 +2718,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,29 +2739,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127802463</v>
+        <v>127802539</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>79061</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,42 +2768,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481355</v>
+        <v>481318</v>
       </c>
       <c r="R21" t="n">
-        <v>6791722</v>
+        <v>6791660</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,7 +2835,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre hackmärken i gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,6 +2844,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2863,45 +2863,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127793514</v>
+        <v>127794064</v>
       </c>
       <c r="B22" t="n">
-        <v>91306</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481353</v>
+        <v>481385</v>
       </c>
       <c r="R22" t="n">
-        <v>6791723</v>
+        <v>6791690</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2970,50 +2975,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127794064</v>
+        <v>127793514</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>91314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481385</v>
+        <v>481353</v>
       </c>
       <c r="R23" t="n">
-        <v>6791690</v>
+        <v>6791723</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127793434</v>
+        <v>127795114</v>
       </c>
       <c r="B24" t="n">
         <v>8450</v>
@@ -3113,7 +3113,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481316</v>
+        <v>481235</v>
       </c>
       <c r="R24" t="n">
-        <v>6791716</v>
+        <v>6791533</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3194,7 +3194,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127795114</v>
+        <v>127793434</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3225,7 +3225,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481235</v>
+        <v>481316</v>
       </c>
       <c r="R25" t="n">
-        <v>6791533</v>
+        <v>6791716</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3306,10 +3306,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127794379</v>
+        <v>127802326</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,37 +3317,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481338</v>
+        <v>481261</v>
       </c>
       <c r="R26" t="n">
-        <v>6791608</v>
+        <v>6791722</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3374,19 +3377,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,28 +3393,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127802326</v>
+        <v>127794379</v>
       </c>
       <c r="B27" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3424,40 +3423,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481261</v>
+        <v>481338</v>
       </c>
       <c r="R27" t="n">
-        <v>6791722</v>
+        <v>6791608</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3484,14 +3480,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,29 +3501,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127794470</v>
+        <v>127794518</v>
       </c>
       <c r="B28" t="n">
-        <v>56858</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,27 +3530,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3605,11 +3605,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127794518</v>
+        <v>127794470</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,27 +3642,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3722,6 +3717,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,7 +3751,7 @@
         <v>127801926</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>127802054</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>127802179</v>
       </c>
       <c r="B32" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>127801947</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127802625</v>
+        <v>127794572</v>
       </c>
       <c r="B34" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,40 +4168,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481275</v>
+        <v>481322</v>
       </c>
       <c r="R34" t="n">
-        <v>6791557</v>
+        <v>6791606</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,14 +4225,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,29 +4246,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802354</v>
+        <v>127802625</v>
       </c>
       <c r="B35" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4301,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481294</v>
+        <v>481275</v>
       </c>
       <c r="R35" t="n">
-        <v>6791733</v>
+        <v>6791557</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4369,10 +4370,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127802650</v>
+        <v>127802354</v>
       </c>
       <c r="B36" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4407,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481248</v>
+        <v>481294</v>
       </c>
       <c r="R36" t="n">
-        <v>6791582</v>
+        <v>6791733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4475,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127794572</v>
+        <v>127802650</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,37 +4487,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481322</v>
+        <v>481248</v>
       </c>
       <c r="R37" t="n">
-        <v>6791606</v>
+        <v>6791582</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4543,19 +4547,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4564,18 +4563,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>127794339</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,17 +4687,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127794182</v>
+        <v>127802041</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,46 +4705,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481374</v>
+        <v>481251</v>
       </c>
       <c r="R39" t="n">
-        <v>6791645</v>
+        <v>6791716</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4771,27 +4765,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4803,64 +4788,64 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127802504</v>
+        <v>127794182</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481325</v>
+        <v>481374</v>
       </c>
       <c r="R40" t="n">
-        <v>6791701</v>
+        <v>6791645</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4887,78 +4872,93 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127802041</v>
+        <v>127802504</v>
       </c>
       <c r="B41" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481251</v>
+        <v>481325</v>
       </c>
       <c r="R41" t="n">
-        <v>6791716</v>
+        <v>6791701</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,12 +5006,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
         <v>127795149</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>127795235</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>127802033</v>
       </c>
       <c r="B44" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>127802418</v>
       </c>
       <c r="B46" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>127792736</v>
       </c>
       <c r="B47" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127802578</v>
+        <v>127801956</v>
       </c>
       <c r="B49" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5781,21 +5781,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5804,14 +5804,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481315</v>
+        <v>481214</v>
       </c>
       <c r="R49" t="n">
-        <v>6791571</v>
+        <v>6791711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,11 +5846,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5864,22 +5859,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127801956</v>
+        <v>127802109</v>
       </c>
       <c r="B50" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5914,10 +5909,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481214</v>
+        <v>481301</v>
       </c>
       <c r="R50" t="n">
-        <v>6791711</v>
+        <v>6791736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5977,10 +5972,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127802109</v>
+        <v>127802578</v>
       </c>
       <c r="B51" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5988,21 +5983,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6011,14 +6006,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481301</v>
+        <v>481315</v>
       </c>
       <c r="R51" t="n">
-        <v>6791736</v>
+        <v>6791571</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6053,6 +6048,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6066,12 +6066,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6081,7 +6081,7 @@
         <v>127802018</v>
       </c>
       <c r="B52" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>127793494</v>
       </c>
       <c r="B53" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>127793626</v>
       </c>
       <c r="B54" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>127802564</v>
       </c>
       <c r="B55" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>127802064</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>127796163</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>127793176</v>
       </c>
       <c r="B58" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>127802522</v>
       </c>
       <c r="B59" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>127793847</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>127802028</v>
       </c>
       <c r="B61" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7138,51 +7138,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127801935</v>
+        <v>127794591</v>
       </c>
       <c r="B62" t="n">
-        <v>92631</v>
+        <v>79061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R62" t="n">
-        <v>6791714</v>
+        <v>6791606</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7209,18 +7206,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7232,17 +7238,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127794591</v>
+        <v>127793724</v>
       </c>
       <c r="B63" t="n">
-        <v>79055</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7250,34 +7256,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481322</v>
+        <v>481344</v>
       </c>
       <c r="R63" t="n">
-        <v>6791606</v>
+        <v>6791702</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7309,7 +7320,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7319,7 +7330,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7346,53 +7357,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127793724</v>
+        <v>127801935</v>
       </c>
       <c r="B64" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481344</v>
+        <v>481193</v>
       </c>
       <c r="R64" t="n">
-        <v>6791702</v>
+        <v>6791714</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7419,27 +7428,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7451,17 +7451,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127802299</v>
+        <v>127802615</v>
       </c>
       <c r="B65" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481213</v>
+        <v>481276</v>
       </c>
       <c r="R65" t="n">
-        <v>6791709</v>
+        <v>6791608</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127802615</v>
+        <v>127801912</v>
       </c>
       <c r="B66" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7575,21 +7575,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7598,14 +7598,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481276</v>
+        <v>481175</v>
       </c>
       <c r="R66" t="n">
-        <v>6791608</v>
+        <v>6791725</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7640,11 +7640,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7658,22 +7653,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127801912</v>
+        <v>127802299</v>
       </c>
       <c r="B67" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7681,21 +7676,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7704,14 +7699,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481175</v>
+        <v>481213</v>
       </c>
       <c r="R67" t="n">
-        <v>6791725</v>
+        <v>6791709</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7746,6 +7741,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,12 +7759,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7774,7 +7774,7 @@
         <v>127794665</v>
       </c>
       <c r="B68" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>127835551</v>
       </c>
       <c r="B69" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>127837613</v>
       </c>
       <c r="B70" t="n">
-        <v>58101</v>
+        <v>58107</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>127836058</v>
       </c>
       <c r="B71" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>127837582</v>
       </c>
       <c r="B72" t="n">
-        <v>57552</v>
+        <v>57558</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127802106</v>
+        <v>127802487</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,14 +1173,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481280</v>
+        <v>481325</v>
       </c>
       <c r="R6" t="n">
-        <v>6791734</v>
+        <v>6791701</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,6 +1215,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1228,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127802487</v>
+        <v>127802106</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,14 +1279,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481325</v>
+        <v>481280</v>
       </c>
       <c r="R7" t="n">
-        <v>6791701</v>
+        <v>6791734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1321,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1334,12 +1334,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
         <v>127795300</v>
       </c>
       <c r="B9" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,53 +1559,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127794366</v>
+        <v>127801964</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481336</v>
+        <v>481215</v>
       </c>
       <c r="R10" t="n">
-        <v>6791622</v>
+        <v>6791716</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,27 +1636,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1664,45 +1659,45 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794623</v>
+        <v>127794366</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1711,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481309</v>
+        <v>481336</v>
       </c>
       <c r="R11" t="n">
-        <v>6791590</v>
+        <v>6791622</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1746,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,7 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,14 +1771,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127801964</v>
+        <v>127794623</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1812,28 +1807,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481215</v>
+        <v>481309</v>
       </c>
       <c r="R12" t="n">
-        <v>6791716</v>
+        <v>6791590</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,18 +1851,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127794298</v>
+        <v>127793859</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481340</v>
+        <v>481377</v>
       </c>
       <c r="R13" t="n">
-        <v>6791650</v>
+        <v>6791659</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127793635</v>
+        <v>127794298</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,39 +2008,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481357</v>
+        <v>481340</v>
       </c>
       <c r="R14" t="n">
-        <v>6791712</v>
+        <v>6791650</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2072,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,10 +2104,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127801929</v>
+        <v>127793635</v>
       </c>
       <c r="B15" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,40 +2115,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481193</v>
+        <v>481357</v>
       </c>
       <c r="R15" t="n">
-        <v>6791718</v>
+        <v>6791712</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,18 +2177,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2203,58 +2209,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127802005</v>
+        <v>127794426</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481219</v>
+        <v>481318</v>
       </c>
       <c r="R16" t="n">
-        <v>6791708</v>
+        <v>6791597</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,18 +2289,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2304,17 +2326,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127802463</v>
+        <v>127801929</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,42 +2344,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481355</v>
+        <v>481193</v>
       </c>
       <c r="R17" t="n">
-        <v>6791722</v>
+        <v>6791718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,36 +2409,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken i gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127793859</v>
+        <v>127802539</v>
       </c>
       <c r="B18" t="n">
         <v>79061</v>
@@ -2450,19 +2463,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481377</v>
+        <v>481318</v>
       </c>
       <c r="R18" t="n">
-        <v>6791659</v>
+        <v>6791660</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2489,19 +2505,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,71 +2521,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127794426</v>
+        <v>127802005</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481318</v>
+        <v>481219</v>
       </c>
       <c r="R19" t="n">
-        <v>6791597</v>
+        <v>6791708</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,32 +2611,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2638,60 +2634,63 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127795085</v>
+        <v>127802463</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481240</v>
+        <v>481355</v>
       </c>
       <c r="R20" t="n">
-        <v>6791516</v>
+        <v>6791722</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2718,19 +2717,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,63 +2739,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127802539</v>
+        <v>127795085</v>
       </c>
       <c r="B21" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481318</v>
+        <v>481240</v>
       </c>
       <c r="R21" t="n">
-        <v>6791660</v>
+        <v>6791516</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2828,14 +2824,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,19 +2845,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
         <v>127793514</v>
       </c>
       <c r="B23" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,53 +3082,51 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127795114</v>
+        <v>127802326</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481235</v>
+        <v>481261</v>
       </c>
       <c r="R24" t="n">
-        <v>6791533</v>
+        <v>6791722</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3155,19 +3153,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,68 +3169,64 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127793434</v>
+        <v>127794379</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481316</v>
+        <v>481338</v>
       </c>
       <c r="R25" t="n">
-        <v>6791716</v>
+        <v>6791608</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3269,7 +3258,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3279,7 +3268,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3299,58 +3288,60 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127802326</v>
+        <v>127793434</v>
       </c>
       <c r="B26" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481261</v>
+        <v>481316</v>
       </c>
       <c r="R26" t="n">
-        <v>6791722</v>
+        <v>6791716</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3377,14 +3368,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,64 +3389,68 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127794379</v>
+        <v>127795114</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481338</v>
+        <v>481235</v>
       </c>
       <c r="R27" t="n">
-        <v>6791608</v>
+        <v>6791533</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,17 +3512,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127794518</v>
+        <v>127794470</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,27 +3530,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3605,6 +3605,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,10 +3636,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127794470</v>
+        <v>127794518</v>
       </c>
       <c r="B29" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,27 +3647,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3719,11 +3724,6 @@
           <t>11:11</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4687,17 +4687,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127802041</v>
+        <v>127794182</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,40 +4705,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481251</v>
+        <v>481374</v>
       </c>
       <c r="R39" t="n">
-        <v>6791716</v>
+        <v>6791645</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4765,18 +4771,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4788,64 +4803,64 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127794182</v>
+        <v>127802504</v>
       </c>
       <c r="B40" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481374</v>
+        <v>481325</v>
       </c>
       <c r="R40" t="n">
-        <v>6791645</v>
+        <v>6791701</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4872,93 +4887,78 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127802504</v>
+        <v>127802041</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481325</v>
+        <v>481251</v>
       </c>
       <c r="R41" t="n">
-        <v>6791701</v>
+        <v>6791716</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,12 +5006,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5333,53 +5333,51 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127793574</v>
+        <v>127802418</v>
       </c>
       <c r="B45" t="n">
-        <v>5177</v>
+        <v>79618</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481353</v>
+        <v>481333</v>
       </c>
       <c r="R45" t="n">
-        <v>6791723</v>
+        <v>6791733</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,19 +5404,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,69 +5420,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127802418</v>
+        <v>127793574</v>
       </c>
       <c r="B46" t="n">
-        <v>79618</v>
+        <v>5177</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481333</v>
+        <v>481353</v>
       </c>
       <c r="R46" t="n">
-        <v>6791733</v>
+        <v>6791723</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5516,14 +5512,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5532,64 +5533,68 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127792736</v>
+        <v>127794070</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481195</v>
+        <v>481378</v>
       </c>
       <c r="R47" t="n">
-        <v>6791715</v>
+        <v>6791650</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5621,7 +5626,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5631,7 +5636,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5658,50 +5663,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127794070</v>
+        <v>127792736</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481378</v>
+        <v>481195</v>
       </c>
       <c r="R48" t="n">
-        <v>6791650</v>
+        <v>6791715</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127801956</v>
+        <v>127802578</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5781,21 +5781,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5804,14 +5804,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481214</v>
+        <v>481315</v>
       </c>
       <c r="R49" t="n">
-        <v>6791711</v>
+        <v>6791571</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,6 +5846,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5859,19 +5864,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127802109</v>
+        <v>127801956</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5909,10 +5914,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481301</v>
+        <v>481214</v>
       </c>
       <c r="R50" t="n">
-        <v>6791736</v>
+        <v>6791711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5972,10 +5977,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127802578</v>
+        <v>127802109</v>
       </c>
       <c r="B51" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5983,21 +5988,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6006,14 +6011,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481315</v>
+        <v>481301</v>
       </c>
       <c r="R51" t="n">
-        <v>6791571</v>
+        <v>6791736</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,11 +6053,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6066,22 +6066,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127802018</v>
+        <v>127793494</v>
       </c>
       <c r="B52" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6089,40 +6089,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481231</v>
+        <v>481328</v>
       </c>
       <c r="R52" t="n">
-        <v>6791714</v>
+        <v>6791735</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6149,18 +6146,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6172,17 +6178,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127793494</v>
+        <v>127793626</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6190,34 +6196,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481328</v>
+        <v>481354</v>
       </c>
       <c r="R53" t="n">
-        <v>6791735</v>
+        <v>6791713</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6286,10 +6297,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127793626</v>
+        <v>127802018</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6297,42 +6308,40 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481354</v>
+        <v>481231</v>
       </c>
       <c r="R54" t="n">
-        <v>6791713</v>
+        <v>6791714</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6359,27 +6368,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6391,17 +6391,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127802564</v>
+        <v>127796163</v>
       </c>
       <c r="B55" t="n">
-        <v>79061</v>
+        <v>57832</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,40 +6409,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481366</v>
+        <v>481305</v>
       </c>
       <c r="R55" t="n">
-        <v>6791657</v>
+        <v>6791432</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6469,14 +6471,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6485,29 +6492,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802064</v>
+        <v>127802564</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6515,21 +6521,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6538,14 +6544,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481273</v>
+        <v>481366</v>
       </c>
       <c r="R56" t="n">
-        <v>6791736</v>
+        <v>6791657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6580,6 +6586,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6593,22 +6604,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127796163</v>
+        <v>127802064</v>
       </c>
       <c r="B57" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6616,42 +6627,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481305</v>
+        <v>481273</v>
       </c>
       <c r="R57" t="n">
-        <v>6791432</v>
+        <v>6791736</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6678,27 +6687,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127794591</v>
+        <v>127793724</v>
       </c>
       <c r="B62" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7149,34 +7149,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481322</v>
+        <v>481344</v>
       </c>
       <c r="R62" t="n">
-        <v>6791606</v>
+        <v>6791702</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7208,7 +7213,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7218,7 +7223,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7245,10 +7250,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127793724</v>
+        <v>127794591</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,39 +7261,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481344</v>
+        <v>481322</v>
       </c>
       <c r="R63" t="n">
-        <v>6791702</v>
+        <v>6791606</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7360,7 +7360,7 @@
         <v>127801935</v>
       </c>
       <c r="B64" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127802615</v>
+        <v>127802299</v>
       </c>
       <c r="B65" t="n">
         <v>79061</v>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481276</v>
+        <v>481213</v>
       </c>
       <c r="R65" t="n">
-        <v>6791608</v>
+        <v>6791709</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127801912</v>
+        <v>127802615</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7575,21 +7575,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7598,14 +7598,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481175</v>
+        <v>481276</v>
       </c>
       <c r="R66" t="n">
-        <v>6791725</v>
+        <v>6791608</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7640,6 +7640,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7653,22 +7658,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127802299</v>
+        <v>127801912</v>
       </c>
       <c r="B67" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7676,21 +7681,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7699,14 +7704,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481213</v>
+        <v>481175</v>
       </c>
       <c r="R67" t="n">
-        <v>6791709</v>
+        <v>6791725</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,11 +7746,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,12 +7759,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -675,67 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127795277</v>
+        <v>127802601</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481286</v>
+        <v>481305</v>
       </c>
       <c r="R2" t="n">
-        <v>6791603</v>
+        <v>6791545</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,24 +751,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stjärtfjäder</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,68 +773,79 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127802601</v>
+        <v>127795277</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481305</v>
+        <v>481286</v>
       </c>
       <c r="R3" t="n">
-        <v>6791545</v>
+        <v>6791603</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,14 +872,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Stjärtfjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127794232</v>
+        <v>127794033</v>
       </c>
       <c r="B4" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,34 +927,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481340</v>
+        <v>481385</v>
       </c>
       <c r="R4" t="n">
-        <v>6791650</v>
+        <v>6791690</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -986,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127794033</v>
+        <v>127802487</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,46 +1043,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481385</v>
+        <v>481325</v>
       </c>
       <c r="R5" t="n">
-        <v>6791690</v>
+        <v>6791701</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,19 +1103,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,28 +1119,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127802487</v>
+        <v>127802106</v>
       </c>
       <c r="B6" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,14 +1172,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481325</v>
+        <v>481280</v>
       </c>
       <c r="R6" t="n">
-        <v>6791701</v>
+        <v>6791734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,11 +1214,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1233,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127802106</v>
+        <v>127802239</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,14 +1273,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481280</v>
+        <v>481187</v>
       </c>
       <c r="R7" t="n">
-        <v>6791734</v>
+        <v>6791714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,6 +1315,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en brändstubbe</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1334,22 +1333,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127802239</v>
+        <v>127794232</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,40 +1356,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481187</v>
+        <v>481340</v>
       </c>
       <c r="R8" t="n">
-        <v>6791714</v>
+        <v>6791650</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,14 +1413,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en brändstubbe</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,64 +1434,68 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127795300</v>
+        <v>127794366</v>
       </c>
       <c r="B9" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481286</v>
+        <v>481336</v>
       </c>
       <c r="R9" t="n">
-        <v>6791603</v>
+        <v>6791622</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,50 +1671,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794366</v>
+        <v>127795300</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481336</v>
+        <v>481286</v>
       </c>
       <c r="R11" t="n">
-        <v>6791622</v>
+        <v>6791603</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127802005</v>
+        <v>127802463</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,37 +2551,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481219</v>
+        <v>481355</v>
       </c>
       <c r="R19" t="n">
-        <v>6791708</v>
+        <v>6791722</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,35 +2621,39 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127802463</v>
+        <v>127802005</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,42 +2661,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481355</v>
+        <v>481219</v>
       </c>
       <c r="R20" t="n">
-        <v>6791722</v>
+        <v>6791708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,29 +2726,25 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken i gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2863,50 +2863,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127794064</v>
+        <v>127793514</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>91315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481385</v>
+        <v>481353</v>
       </c>
       <c r="R22" t="n">
-        <v>6791690</v>
+        <v>6791723</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2975,45 +2970,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127793514</v>
+        <v>127794064</v>
       </c>
       <c r="B23" t="n">
-        <v>91315</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481353</v>
+        <v>481385</v>
       </c>
       <c r="R23" t="n">
-        <v>6791723</v>
+        <v>6791690</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127802326</v>
+        <v>127794379</v>
       </c>
       <c r="B24" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,40 +3093,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481261</v>
+        <v>481338</v>
       </c>
       <c r="R24" t="n">
-        <v>6791722</v>
+        <v>6791608</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3153,14 +3150,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,64 +3171,68 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127794379</v>
+        <v>127793434</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481338</v>
+        <v>481316</v>
       </c>
       <c r="R25" t="n">
-        <v>6791608</v>
+        <v>6791716</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3258,7 +3264,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3268,7 +3274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3295,7 +3301,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127793434</v>
+        <v>127795114</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3326,7 +3332,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3335,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481316</v>
+        <v>481235</v>
       </c>
       <c r="R26" t="n">
-        <v>6791716</v>
+        <v>6791533</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3370,7 +3376,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3386,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,53 +3413,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127795114</v>
+        <v>127802326</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481235</v>
+        <v>481261</v>
       </c>
       <c r="R27" t="n">
-        <v>6791533</v>
+        <v>6791722</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3480,19 +3484,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,71 +3500,70 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127794470</v>
+        <v>127802054</v>
       </c>
       <c r="B28" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481322</v>
+        <v>481267</v>
       </c>
       <c r="R28" t="n">
-        <v>6791606</v>
+        <v>6791723</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3592,32 +3590,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3629,17 +3613,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127794518</v>
+        <v>127794470</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,27 +3631,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3724,6 +3708,11 @@
           <t>11:11</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3741,58 +3730,60 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127801926</v>
+        <v>127794518</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R30" t="n">
-        <v>6791718</v>
+        <v>6791606</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3819,18 +3810,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3842,14 +3842,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127802054</v>
+        <v>127801926</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481267</v>
+        <v>481193</v>
       </c>
       <c r="R31" t="n">
-        <v>6791723</v>
+        <v>6791718</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4810,54 +4810,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127802504</v>
+        <v>127802041</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481325</v>
+        <v>481251</v>
       </c>
       <c r="R40" t="n">
-        <v>6791701</v>
+        <v>6791716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,60 +4899,66 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127802041</v>
+        <v>127802504</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481251</v>
+        <v>481325</v>
       </c>
       <c r="R41" t="n">
-        <v>6791716</v>
+        <v>6791701</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,12 +5006,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5333,51 +5333,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127802418</v>
+        <v>127793574</v>
       </c>
       <c r="B45" t="n">
-        <v>79618</v>
+        <v>5177</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481333</v>
+        <v>481353</v>
       </c>
       <c r="R45" t="n">
-        <v>6791733</v>
+        <v>6791723</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5404,14 +5406,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5420,72 +5427,69 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127793574</v>
+        <v>127802418</v>
       </c>
       <c r="B46" t="n">
-        <v>5177</v>
+        <v>79618</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481353</v>
+        <v>481333</v>
       </c>
       <c r="R46" t="n">
-        <v>6791723</v>
+        <v>6791733</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5512,19 +5516,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5533,18 +5532,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127793494</v>
+        <v>127793626</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6089,34 +6089,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481328</v>
+        <v>481354</v>
       </c>
       <c r="R52" t="n">
-        <v>6791735</v>
+        <v>6791713</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6178,17 +6183,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127793626</v>
+        <v>127793494</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6196,39 +6201,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481354</v>
+        <v>481328</v>
       </c>
       <c r="R53" t="n">
-        <v>6791713</v>
+        <v>6791735</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127796163</v>
+        <v>127802564</v>
       </c>
       <c r="B55" t="n">
-        <v>57832</v>
+        <v>79061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,42 +6409,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481305</v>
+        <v>481366</v>
       </c>
       <c r="R55" t="n">
-        <v>6791432</v>
+        <v>6791657</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6471,19 +6469,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6492,28 +6485,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802564</v>
+        <v>127802064</v>
       </c>
       <c r="B56" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6521,21 +6515,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6544,14 +6538,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481366</v>
+        <v>481273</v>
       </c>
       <c r="R56" t="n">
-        <v>6791657</v>
+        <v>6791736</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6586,11 +6580,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6604,22 +6593,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127802064</v>
+        <v>127796163</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6627,40 +6616,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481273</v>
+        <v>481305</v>
       </c>
       <c r="R57" t="n">
-        <v>6791736</v>
+        <v>6791432</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6687,18 +6678,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127793724</v>
+        <v>127794591</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7149,39 +7149,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481344</v>
+        <v>481322</v>
       </c>
       <c r="R62" t="n">
-        <v>6791702</v>
+        <v>6791606</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7213,7 +7208,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7223,7 +7218,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7243,17 +7238,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127794591</v>
+        <v>127793724</v>
       </c>
       <c r="B63" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7261,34 +7256,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481322</v>
+        <v>481344</v>
       </c>
       <c r="R63" t="n">
-        <v>6791606</v>
+        <v>6791702</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127794623</v>
+        <v>127795300</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,39 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481309</v>
+        <v>481286</v>
       </c>
       <c r="R9" t="n">
-        <v>6791590</v>
+        <v>6791603</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,7 +1671,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127801964</v>
+        <v>127794623</v>
       </c>
       <c r="B11" t="n">
         <v>8450</v>
@@ -1705,28 +1700,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481215</v>
+        <v>481309</v>
       </c>
       <c r="R11" t="n">
-        <v>6791716</v>
+        <v>6791590</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,18 +1744,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127795300</v>
+        <v>127801964</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,37 +1794,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481286</v>
+        <v>481215</v>
       </c>
       <c r="R12" t="n">
-        <v>6791603</v>
+        <v>6791716</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,27 +1860,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,14 +1883,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127793859</v>
+        <v>127801929</v>
       </c>
       <c r="B13" t="n">
         <v>79061</v>
@@ -1919,19 +1919,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481377</v>
+        <v>481193</v>
       </c>
       <c r="R13" t="n">
-        <v>6791659</v>
+        <v>6791718</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,27 +1961,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1990,17 +1984,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127794298</v>
+        <v>127802539</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,37 +2002,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481340</v>
+        <v>481318</v>
       </c>
       <c r="R14" t="n">
-        <v>6791650</v>
+        <v>6791660</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2065,19 +2062,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,28 +2078,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127793635</v>
+        <v>127802005</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,42 +2108,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481357</v>
+        <v>481219</v>
       </c>
       <c r="R15" t="n">
-        <v>6791712</v>
+        <v>6791708</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,27 +2168,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,60 +2191,63 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127794426</v>
+        <v>127802463</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481318</v>
+        <v>481355</v>
       </c>
       <c r="R16" t="n">
-        <v>6791597</v>
+        <v>6791722</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,24 +2274,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,62 +2296,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127795085</v>
+        <v>127793859</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481240</v>
+        <v>481377</v>
       </c>
       <c r="R17" t="n">
-        <v>6791516</v>
+        <v>6791659</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2408,7 +2378,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2388,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127801929</v>
+        <v>127794298</v>
       </c>
       <c r="B18" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,40 +2426,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481193</v>
+        <v>481340</v>
       </c>
       <c r="R18" t="n">
-        <v>6791718</v>
+        <v>6791650</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,18 +2483,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2539,58 +2515,60 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127802539</v>
+        <v>127794426</v>
       </c>
       <c r="B19" t="n">
-        <v>79061</v>
+        <v>56864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>481318</v>
       </c>
       <c r="R19" t="n">
-        <v>6791660</v>
+        <v>6791597</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,14 +2595,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,29 +2621,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127802005</v>
+        <v>127793635</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,40 +2650,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481219</v>
+        <v>481357</v>
       </c>
       <c r="R20" t="n">
-        <v>6791708</v>
+        <v>6791712</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2723,18 +2712,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2746,63 +2744,60 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127802463</v>
+        <v>127795085</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481355</v>
+        <v>481240</v>
       </c>
       <c r="R21" t="n">
-        <v>6791722</v>
+        <v>6791516</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2829,14 +2824,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken i gran</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,12 +2851,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127802625</v>
+        <v>127794572</v>
       </c>
       <c r="B34" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,40 +4168,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481275</v>
+        <v>481322</v>
       </c>
       <c r="R34" t="n">
-        <v>6791557</v>
+        <v>6791606</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,14 +4225,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,26 +4246,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802354</v>
+        <v>127802625</v>
       </c>
       <c r="B35" t="n">
         <v>79061</v>
@@ -4301,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481294</v>
+        <v>481275</v>
       </c>
       <c r="R35" t="n">
-        <v>6791733</v>
+        <v>6791557</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4369,7 +4370,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127802650</v>
+        <v>127802354</v>
       </c>
       <c r="B36" t="n">
         <v>79061</v>
@@ -4407,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481248</v>
+        <v>481294</v>
       </c>
       <c r="R36" t="n">
-        <v>6791582</v>
+        <v>6791733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4475,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127794572</v>
+        <v>127802650</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,37 +4487,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481322</v>
+        <v>481248</v>
       </c>
       <c r="R37" t="n">
-        <v>6791606</v>
+        <v>6791582</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4543,19 +4547,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4564,18 +4563,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127793494</v>
+        <v>127802018</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6089,37 +6089,40 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481328</v>
+        <v>481231</v>
       </c>
       <c r="R52" t="n">
-        <v>6791735</v>
+        <v>6791714</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6146,27 +6149,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6178,17 +6172,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127793626</v>
+        <v>127793494</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6196,39 +6190,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481354</v>
+        <v>481328</v>
       </c>
       <c r="R53" t="n">
-        <v>6791713</v>
+        <v>6791735</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6297,10 +6286,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127802018</v>
+        <v>127793626</v>
       </c>
       <c r="B54" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6308,40 +6297,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481231</v>
+        <v>481354</v>
       </c>
       <c r="R54" t="n">
-        <v>6791714</v>
+        <v>6791713</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6368,18 +6359,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6391,17 +6391,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127802564</v>
+        <v>127796163</v>
       </c>
       <c r="B55" t="n">
-        <v>79061</v>
+        <v>57832</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,40 +6409,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481366</v>
+        <v>481305</v>
       </c>
       <c r="R55" t="n">
-        <v>6791657</v>
+        <v>6791432</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6469,14 +6471,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6485,29 +6492,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802064</v>
+        <v>127802564</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6515,21 +6521,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6538,14 +6544,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481273</v>
+        <v>481366</v>
       </c>
       <c r="R56" t="n">
-        <v>6791736</v>
+        <v>6791657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6580,6 +6586,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6593,22 +6604,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127796163</v>
+        <v>127802064</v>
       </c>
       <c r="B57" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6616,42 +6627,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481305</v>
+        <v>481273</v>
       </c>
       <c r="R57" t="n">
-        <v>6791432</v>
+        <v>6791736</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6678,27 +6687,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127802299</v>
+        <v>127801912</v>
       </c>
       <c r="B65" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,14 +7492,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481213</v>
+        <v>481175</v>
       </c>
       <c r="R65" t="n">
-        <v>6791709</v>
+        <v>6791725</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,11 +7534,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7552,19 +7547,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127802615</v>
+        <v>127802299</v>
       </c>
       <c r="B66" t="n">
         <v>79061</v>
@@ -7602,10 +7597,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481276</v>
+        <v>481213</v>
       </c>
       <c r="R66" t="n">
-        <v>6791608</v>
+        <v>6791709</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7670,10 +7665,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127801912</v>
+        <v>127802615</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7681,21 +7676,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7704,14 +7699,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481175</v>
+        <v>481276</v>
       </c>
       <c r="R67" t="n">
-        <v>6791725</v>
+        <v>6791608</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7746,6 +7741,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,12 +7759,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -675,67 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127795277</v>
+        <v>127802601</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481286</v>
+        <v>481305</v>
       </c>
       <c r="R2" t="n">
-        <v>6791603</v>
+        <v>6791545</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,24 +751,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stjärtfjäder</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,68 +773,79 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127802601</v>
+        <v>127795277</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481305</v>
+        <v>481286</v>
       </c>
       <c r="R3" t="n">
-        <v>6791545</v>
+        <v>6791603</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,14 +872,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Stjärtfjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802106</v>
+        <v>127802487</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,14 +950,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481280</v>
+        <v>481325</v>
       </c>
       <c r="R4" t="n">
-        <v>6791734</v>
+        <v>6791701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +992,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127794232</v>
+        <v>127802106</v>
       </c>
       <c r="B5" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,37 +1033,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481340</v>
+        <v>481280</v>
       </c>
       <c r="R5" t="n">
-        <v>6791650</v>
+        <v>6791734</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,27 +1093,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,17 +1116,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127794033</v>
+        <v>127794232</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,43 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481385</v>
+        <v>481340</v>
       </c>
       <c r="R6" t="n">
-        <v>6791690</v>
+        <v>6791650</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1203,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127802487</v>
+        <v>127794033</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,40 +1241,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481325</v>
+        <v>481385</v>
       </c>
       <c r="R7" t="n">
-        <v>6791701</v>
+        <v>6791690</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,14 +1307,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,19 +1328,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127795300</v>
+        <v>127794623</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1463,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481286</v>
+        <v>481309</v>
       </c>
       <c r="R9" t="n">
-        <v>6791603</v>
+        <v>6791590</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,7 +1676,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794623</v>
+        <v>127801964</v>
       </c>
       <c r="B11" t="n">
         <v>8450</v>
@@ -1700,24 +1705,28 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481309</v>
+        <v>481215</v>
       </c>
       <c r="R11" t="n">
-        <v>6791590</v>
+        <v>6791716</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,27 +1753,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127801964</v>
+        <v>127795300</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,46 +1794,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481215</v>
+        <v>481286</v>
       </c>
       <c r="R12" t="n">
-        <v>6791716</v>
+        <v>6791603</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,18 +1851,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,14 +1883,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127801929</v>
+        <v>127793859</v>
       </c>
       <c r="B13" t="n">
         <v>79061</v>
@@ -1919,22 +1919,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481193</v>
+        <v>481377</v>
       </c>
       <c r="R13" t="n">
-        <v>6791718</v>
+        <v>6791659</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,18 +1958,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,17 +1990,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127802539</v>
+        <v>127794298</v>
       </c>
       <c r="B14" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,40 +2008,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481318</v>
+        <v>481340</v>
       </c>
       <c r="R14" t="n">
-        <v>6791660</v>
+        <v>6791650</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,14 +2065,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,29 +2086,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127802005</v>
+        <v>127793635</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,40 +2115,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481219</v>
+        <v>481357</v>
       </c>
       <c r="R15" t="n">
-        <v>6791708</v>
+        <v>6791712</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2168,18 +2177,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2191,63 +2209,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127802463</v>
+        <v>127794426</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481355</v>
+        <v>481318</v>
       </c>
       <c r="R16" t="n">
-        <v>6791722</v>
+        <v>6791597</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,14 +2289,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre hackmärken i gran</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,57 +2321,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127793859</v>
+        <v>127795085</v>
       </c>
       <c r="B17" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481377</v>
+        <v>481240</v>
       </c>
       <c r="R17" t="n">
-        <v>6791659</v>
+        <v>6791516</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2378,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2388,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127794298</v>
+        <v>127801929</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,37 +2456,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481340</v>
+        <v>481193</v>
       </c>
       <c r="R18" t="n">
-        <v>6791650</v>
+        <v>6791718</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,27 +2516,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2515,60 +2539,58 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127794426</v>
+        <v>127802539</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>79061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>481318</v>
       </c>
       <c r="R19" t="n">
-        <v>6791597</v>
+        <v>6791660</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2595,24 +2617,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,28 +2633,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127793635</v>
+        <v>127802005</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,42 +2663,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481357</v>
+        <v>481219</v>
       </c>
       <c r="R20" t="n">
-        <v>6791712</v>
+        <v>6791708</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2712,27 +2723,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2744,60 +2746,63 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127795085</v>
+        <v>127802463</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481240</v>
+        <v>481355</v>
       </c>
       <c r="R21" t="n">
-        <v>6791516</v>
+        <v>6791722</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2824,19 +2829,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,12 +2851,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3189,51 +3189,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127802326</v>
+        <v>127793434</v>
       </c>
       <c r="B25" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481261</v>
+        <v>481316</v>
       </c>
       <c r="R25" t="n">
-        <v>6791722</v>
+        <v>6791716</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3260,14 +3262,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,26 +3283,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127793434</v>
+        <v>127795114</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3326,7 +3332,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3335,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481316</v>
+        <v>481235</v>
       </c>
       <c r="R26" t="n">
-        <v>6791716</v>
+        <v>6791533</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3370,7 +3376,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3386,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,53 +3413,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127795114</v>
+        <v>127802326</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481235</v>
+        <v>481261</v>
       </c>
       <c r="R27" t="n">
-        <v>6791533</v>
+        <v>6791722</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3480,19 +3484,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,18 +3500,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127794572</v>
+        <v>127802625</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,37 +4168,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481322</v>
+        <v>481275</v>
       </c>
       <c r="R34" t="n">
-        <v>6791606</v>
+        <v>6791557</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4225,19 +4228,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4246,25 +4244,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802625</v>
+        <v>127802354</v>
       </c>
       <c r="B35" t="n">
         <v>79061</v>
@@ -4302,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481275</v>
+        <v>481294</v>
       </c>
       <c r="R35" t="n">
-        <v>6791557</v>
+        <v>6791733</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,7 +4369,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127802354</v>
+        <v>127802650</v>
       </c>
       <c r="B36" t="n">
         <v>79061</v>
@@ -4408,10 +4407,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481294</v>
+        <v>481248</v>
       </c>
       <c r="R36" t="n">
-        <v>6791733</v>
+        <v>6791582</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127802650</v>
+        <v>127794572</v>
       </c>
       <c r="B37" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,40 +4486,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481248</v>
+        <v>481322</v>
       </c>
       <c r="R37" t="n">
-        <v>6791582</v>
+        <v>6791606</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4547,14 +4543,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4563,19 +4564,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127801912</v>
+        <v>127802299</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,14 +7492,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481175</v>
+        <v>481213</v>
       </c>
       <c r="R65" t="n">
-        <v>6791725</v>
+        <v>6791709</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,6 +7534,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7547,19 +7552,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127802299</v>
+        <v>127802615</v>
       </c>
       <c r="B66" t="n">
         <v>79061</v>
@@ -7597,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481213</v>
+        <v>481276</v>
       </c>
       <c r="R66" t="n">
-        <v>6791709</v>
+        <v>6791608</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7665,10 +7670,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127802615</v>
+        <v>127801912</v>
       </c>
       <c r="B67" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7676,21 +7681,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7699,14 +7704,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481276</v>
+        <v>481175</v>
       </c>
       <c r="R67" t="n">
-        <v>6791608</v>
+        <v>6791725</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,11 +7746,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,12 +7759,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802487</v>
+        <v>127802106</v>
       </c>
       <c r="B4" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,14 +950,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481325</v>
+        <v>481280</v>
       </c>
       <c r="R4" t="n">
-        <v>6791701</v>
+        <v>6791734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,11 +992,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,22 +1005,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127802106</v>
+        <v>127794232</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,40 +1028,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481280</v>
+        <v>481340</v>
       </c>
       <c r="R5" t="n">
-        <v>6791734</v>
+        <v>6791650</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,18 +1085,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,17 +1117,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127794232</v>
+        <v>127794033</v>
       </c>
       <c r="B6" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1135,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481340</v>
+        <v>481385</v>
       </c>
       <c r="R6" t="n">
-        <v>6791650</v>
+        <v>6791690</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1193,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127794033</v>
+        <v>127802487</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,46 +1251,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481385</v>
+        <v>481325</v>
       </c>
       <c r="R7" t="n">
-        <v>6791690</v>
+        <v>6791701</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,19 +1311,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,18 +1327,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127793859</v>
+        <v>127801929</v>
       </c>
       <c r="B13" t="n">
         <v>79061</v>
@@ -1919,19 +1919,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481377</v>
+        <v>481193</v>
       </c>
       <c r="R13" t="n">
-        <v>6791659</v>
+        <v>6791718</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,27 +1961,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1990,17 +1984,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127794298</v>
+        <v>127802539</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,37 +2002,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481340</v>
+        <v>481318</v>
       </c>
       <c r="R14" t="n">
-        <v>6791650</v>
+        <v>6791660</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2065,19 +2062,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,28 +2078,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127793635</v>
+        <v>127802005</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,42 +2108,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481357</v>
+        <v>481219</v>
       </c>
       <c r="R15" t="n">
-        <v>6791712</v>
+        <v>6791708</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,27 +2168,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,60 +2191,63 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127794426</v>
+        <v>127802463</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481318</v>
+        <v>481355</v>
       </c>
       <c r="R16" t="n">
-        <v>6791597</v>
+        <v>6791722</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,24 +2274,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,62 +2296,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127795085</v>
+        <v>127793859</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481240</v>
+        <v>481377</v>
       </c>
       <c r="R17" t="n">
-        <v>6791516</v>
+        <v>6791659</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2408,7 +2378,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2388,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127801929</v>
+        <v>127794298</v>
       </c>
       <c r="B18" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,40 +2426,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481193</v>
+        <v>481340</v>
       </c>
       <c r="R18" t="n">
-        <v>6791718</v>
+        <v>6791650</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,18 +2483,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2539,58 +2515,60 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127802539</v>
+        <v>127794426</v>
       </c>
       <c r="B19" t="n">
-        <v>79061</v>
+        <v>56864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>481318</v>
       </c>
       <c r="R19" t="n">
-        <v>6791660</v>
+        <v>6791597</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,14 +2595,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,29 +2621,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127802005</v>
+        <v>127793635</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,40 +2650,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481219</v>
+        <v>481357</v>
       </c>
       <c r="R20" t="n">
-        <v>6791708</v>
+        <v>6791712</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2723,18 +2712,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2746,63 +2744,60 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127802463</v>
+        <v>127795085</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481355</v>
+        <v>481240</v>
       </c>
       <c r="R21" t="n">
-        <v>6791722</v>
+        <v>6791516</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2829,14 +2824,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken i gran</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,12 +2851,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3189,53 +3189,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127793434</v>
+        <v>127802326</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481316</v>
+        <v>481261</v>
       </c>
       <c r="R25" t="n">
-        <v>6791716</v>
+        <v>6791722</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3262,19 +3260,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:04</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3283,25 +3276,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127795114</v>
+        <v>127793434</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3332,7 +3326,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3341,10 +3335,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481235</v>
+        <v>481316</v>
       </c>
       <c r="R26" t="n">
-        <v>6791533</v>
+        <v>6791716</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3376,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3386,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3413,51 +3407,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127802326</v>
+        <v>127795114</v>
       </c>
       <c r="B27" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481261</v>
+        <v>481235</v>
       </c>
       <c r="R27" t="n">
-        <v>6791722</v>
+        <v>6791533</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3484,14 +3480,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,19 +3501,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127794470</v>
+        <v>127794518</v>
       </c>
       <c r="B30" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3732,27 +3732,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3807,11 +3807,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,10 +3833,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127794518</v>
+        <v>127794470</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3849,27 +3844,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3924,6 +3919,11 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4157,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127802625</v>
+        <v>127794572</v>
       </c>
       <c r="B34" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,40 +4168,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481275</v>
+        <v>481322</v>
       </c>
       <c r="R34" t="n">
-        <v>6791557</v>
+        <v>6791606</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,14 +4225,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,26 +4246,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802354</v>
+        <v>127802625</v>
       </c>
       <c r="B35" t="n">
         <v>79061</v>
@@ -4301,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481294</v>
+        <v>481275</v>
       </c>
       <c r="R35" t="n">
-        <v>6791733</v>
+        <v>6791557</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4369,7 +4370,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127802650</v>
+        <v>127802354</v>
       </c>
       <c r="B36" t="n">
         <v>79061</v>
@@ -4407,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481248</v>
+        <v>481294</v>
       </c>
       <c r="R36" t="n">
-        <v>6791582</v>
+        <v>6791733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4475,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127794572</v>
+        <v>127802650</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,37 +4487,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481322</v>
+        <v>481248</v>
       </c>
       <c r="R37" t="n">
-        <v>6791606</v>
+        <v>6791582</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4543,19 +4547,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4564,71 +4563,76 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127794339</v>
+        <v>127802504</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481340</v>
+        <v>481325</v>
       </c>
       <c r="R38" t="n">
-        <v>6791650</v>
+        <v>6791701</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4655,49 +4659,40 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127794182</v>
+        <v>127794339</v>
       </c>
       <c r="B39" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,31 +4700,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4738,10 +4729,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481374</v>
+        <v>481340</v>
       </c>
       <c r="R39" t="n">
-        <v>6791645</v>
+        <v>6791650</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4810,57 +4801,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127802504</v>
+        <v>127794182</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481325</v>
+        <v>481374</v>
       </c>
       <c r="R40" t="n">
-        <v>6791701</v>
+        <v>6791645</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4887,30 +4878,39 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127802033</v>
+        <v>127795149</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -5047,22 +5047,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481244</v>
+        <v>481247</v>
       </c>
       <c r="R42" t="n">
-        <v>6791710</v>
+        <v>6791558</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5089,18 +5086,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5112,14 +5118,14 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127795149</v>
+        <v>127795235</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5154,10 +5160,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481247</v>
+        <v>481286</v>
       </c>
       <c r="R43" t="n">
-        <v>6791558</v>
+        <v>6791603</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5189,7 +5195,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5205,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5232,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127795235</v>
+        <v>127802033</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -5255,19 +5261,22 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481286</v>
+        <v>481244</v>
       </c>
       <c r="R44" t="n">
-        <v>6791603</v>
+        <v>6791710</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5294,27 +5303,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127802018</v>
+        <v>127793494</v>
       </c>
       <c r="B52" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6089,40 +6089,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481231</v>
+        <v>481328</v>
       </c>
       <c r="R52" t="n">
-        <v>6791714</v>
+        <v>6791735</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6149,18 +6146,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6172,17 +6178,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127793494</v>
+        <v>127793626</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6190,34 +6196,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481328</v>
+        <v>481354</v>
       </c>
       <c r="R53" t="n">
-        <v>6791735</v>
+        <v>6791713</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6286,10 +6297,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127793626</v>
+        <v>127802018</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6297,42 +6308,40 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481354</v>
+        <v>481231</v>
       </c>
       <c r="R54" t="n">
-        <v>6791713</v>
+        <v>6791714</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6359,27 +6368,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6391,17 +6391,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127796163</v>
+        <v>127802564</v>
       </c>
       <c r="B55" t="n">
-        <v>57832</v>
+        <v>79061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,42 +6409,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481305</v>
+        <v>481366</v>
       </c>
       <c r="R55" t="n">
-        <v>6791432</v>
+        <v>6791657</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6471,19 +6469,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6492,28 +6485,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802564</v>
+        <v>127802064</v>
       </c>
       <c r="B56" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6521,21 +6515,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6544,14 +6538,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481366</v>
+        <v>481273</v>
       </c>
       <c r="R56" t="n">
-        <v>6791657</v>
+        <v>6791736</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6586,11 +6580,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6604,22 +6593,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127802064</v>
+        <v>127796163</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6627,40 +6616,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481273</v>
+        <v>481305</v>
       </c>
       <c r="R57" t="n">
-        <v>6791736</v>
+        <v>6791432</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6687,18 +6678,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127802299</v>
+        <v>127801912</v>
       </c>
       <c r="B65" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,14 +7492,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481213</v>
+        <v>481175</v>
       </c>
       <c r="R65" t="n">
-        <v>6791709</v>
+        <v>6791725</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,11 +7534,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7552,19 +7547,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127802615</v>
+        <v>127802299</v>
       </c>
       <c r="B66" t="n">
         <v>79061</v>
@@ -7602,10 +7597,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481276</v>
+        <v>481213</v>
       </c>
       <c r="R66" t="n">
-        <v>6791608</v>
+        <v>6791709</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7670,10 +7665,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127801912</v>
+        <v>127802615</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7681,21 +7676,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7704,14 +7699,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481175</v>
+        <v>481276</v>
       </c>
       <c r="R67" t="n">
-        <v>6791725</v>
+        <v>6791608</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7746,6 +7741,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,12 +7759,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127802601</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802106</v>
+        <v>127802239</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,14 +950,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481280</v>
+        <v>481187</v>
       </c>
       <c r="R4" t="n">
-        <v>6791734</v>
+        <v>6791714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +992,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en brändstubbe</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127794232</v>
+        <v>127794033</v>
       </c>
       <c r="B5" t="n">
-        <v>79061</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,34 +1033,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481340</v>
+        <v>481385</v>
       </c>
       <c r="R5" t="n">
-        <v>6791650</v>
+        <v>6791690</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1087,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127794033</v>
+        <v>127794232</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>79064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,43 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481385</v>
+        <v>481340</v>
       </c>
       <c r="R6" t="n">
-        <v>6791690</v>
+        <v>6791650</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127802487</v>
+        <v>127802106</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,14 +1279,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481325</v>
+        <v>481280</v>
       </c>
       <c r="R7" t="n">
-        <v>6791701</v>
+        <v>6791734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1321,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1334,22 +1334,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127802239</v>
+        <v>127802487</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481187</v>
+        <v>481325</v>
       </c>
       <c r="R8" t="n">
-        <v>6791714</v>
+        <v>6791701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en brändstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127794623</v>
+        <v>127801964</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1481,24 +1481,28 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481309</v>
+        <v>481215</v>
       </c>
       <c r="R9" t="n">
-        <v>6791590</v>
+        <v>6791716</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,27 +1529,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1557,45 +1552,45 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127794366</v>
+        <v>127794623</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481336</v>
+        <v>481309</v>
       </c>
       <c r="R10" t="n">
-        <v>6791622</v>
+        <v>6791590</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127801964</v>
+        <v>127795300</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,46 +1682,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481215</v>
+        <v>481286</v>
       </c>
       <c r="R11" t="n">
-        <v>6791716</v>
+        <v>6791603</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,18 +1739,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,52 +1771,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127795300</v>
+        <v>127794366</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481286</v>
+        <v>481336</v>
       </c>
       <c r="R12" t="n">
-        <v>6791603</v>
+        <v>6791622</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127801929</v>
+        <v>127793859</v>
       </c>
       <c r="B13" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,22 +1919,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481193</v>
+        <v>481377</v>
       </c>
       <c r="R13" t="n">
-        <v>6791718</v>
+        <v>6791659</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,18 +1958,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,17 +1990,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127802539</v>
+        <v>127802005</v>
       </c>
       <c r="B14" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2025,14 +2031,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481318</v>
+        <v>481219</v>
       </c>
       <c r="R14" t="n">
-        <v>6791660</v>
+        <v>6791708</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,11 +2073,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2085,22 +2086,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127802005</v>
+        <v>127801929</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,21 +2109,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481219</v>
+        <v>481193</v>
       </c>
       <c r="R15" t="n">
-        <v>6791708</v>
+        <v>6791718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127802463</v>
+        <v>127802539</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>79064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,42 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481355</v>
+        <v>481318</v>
       </c>
       <c r="R16" t="n">
-        <v>6791722</v>
+        <v>6791660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre hackmärken i gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,6 +2286,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2308,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127793859</v>
+        <v>127802463</v>
       </c>
       <c r="B17" t="n">
-        <v>79061</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,37 +2316,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481377</v>
+        <v>481355</v>
       </c>
       <c r="R17" t="n">
-        <v>6791659</v>
+        <v>6791722</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2376,19 +2381,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,57 +2403,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127794298</v>
+        <v>127794426</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481340</v>
+        <v>481318</v>
       </c>
       <c r="R18" t="n">
-        <v>6791650</v>
+        <v>6791597</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2485,7 +2490,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2495,7 +2500,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,38 +2532,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127794426</v>
+        <v>127793635</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2562,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481318</v>
+        <v>481357</v>
       </c>
       <c r="R19" t="n">
-        <v>6791597</v>
+        <v>6791712</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2597,7 +2607,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2607,12 +2617,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,38 +2644,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127793635</v>
+        <v>127795085</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2679,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481357</v>
+        <v>481240</v>
       </c>
       <c r="R20" t="n">
-        <v>6791712</v>
+        <v>6791516</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2714,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2724,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,50 +2756,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127795085</v>
+        <v>127794298</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481240</v>
+        <v>481340</v>
       </c>
       <c r="R21" t="n">
-        <v>6791516</v>
+        <v>6791650</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,45 +2863,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127793514</v>
+        <v>127794064</v>
       </c>
       <c r="B22" t="n">
-        <v>91317</v>
+        <v>57670</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481353</v>
+        <v>481385</v>
       </c>
       <c r="R22" t="n">
-        <v>6791723</v>
+        <v>6791690</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2970,50 +2975,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127794064</v>
+        <v>127793514</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>91325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481385</v>
+        <v>481353</v>
       </c>
       <c r="R23" t="n">
-        <v>6791690</v>
+        <v>6791723</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3082,45 +3082,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127794379</v>
+        <v>127793434</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481338</v>
+        <v>481316</v>
       </c>
       <c r="R24" t="n">
-        <v>6791608</v>
+        <v>6791716</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3152,7 +3157,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3167,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,51 +3194,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127802326</v>
+        <v>127795114</v>
       </c>
       <c r="B25" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481261</v>
+        <v>481235</v>
       </c>
       <c r="R25" t="n">
-        <v>6791722</v>
+        <v>6791533</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3260,14 +3267,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,72 +3288,69 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127793434</v>
+        <v>127802326</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481316</v>
+        <v>481261</v>
       </c>
       <c r="R26" t="n">
-        <v>6791716</v>
+        <v>6791722</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3368,19 +3377,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:04</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,68 +3393,64 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127795114</v>
+        <v>127794379</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481235</v>
+        <v>481338</v>
       </c>
       <c r="R27" t="n">
-        <v>6791533</v>
+        <v>6791608</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3519,51 +3519,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127802054</v>
+        <v>127794470</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481267</v>
+        <v>481322</v>
       </c>
       <c r="R28" t="n">
-        <v>6791723</v>
+        <v>6791606</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,18 +3592,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3613,58 +3629,60 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127801926</v>
+        <v>127794518</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R29" t="n">
-        <v>6791718</v>
+        <v>6791606</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3691,18 +3709,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3714,60 +3741,58 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127794518</v>
+        <v>127801926</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481322</v>
+        <v>481193</v>
       </c>
       <c r="R30" t="n">
-        <v>6791606</v>
+        <v>6791718</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3794,27 +3819,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3826,60 +3842,58 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127794470</v>
+        <v>127802054</v>
       </c>
       <c r="B31" t="n">
-        <v>56864</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481322</v>
+        <v>481267</v>
       </c>
       <c r="R31" t="n">
-        <v>6791606</v>
+        <v>6791723</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3906,32 +3920,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3943,17 +3943,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127802179</v>
+        <v>127801947</v>
       </c>
       <c r="B32" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,21 +3961,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,14 +3984,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481186</v>
+        <v>481204</v>
       </c>
       <c r="R32" t="n">
-        <v>6791726</v>
+        <v>6791711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4026,11 +4026,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4044,22 +4039,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127801947</v>
+        <v>127802179</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79064</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4090,14 +4085,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481204</v>
+        <v>481186</v>
       </c>
       <c r="R33" t="n">
-        <v>6791711</v>
+        <v>6791726</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4132,6 +4127,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4145,22 +4145,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127794572</v>
+        <v>127802625</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,37 +4168,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481322</v>
+        <v>481275</v>
       </c>
       <c r="R34" t="n">
-        <v>6791606</v>
+        <v>6791557</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4225,19 +4228,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4246,28 +4244,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802625</v>
+        <v>127802354</v>
       </c>
       <c r="B35" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4302,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481275</v>
+        <v>481294</v>
       </c>
       <c r="R35" t="n">
-        <v>6791557</v>
+        <v>6791733</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,10 +4369,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127802354</v>
+        <v>127802650</v>
       </c>
       <c r="B36" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4408,10 +4407,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481294</v>
+        <v>481248</v>
       </c>
       <c r="R36" t="n">
-        <v>6791733</v>
+        <v>6791582</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127802650</v>
+        <v>127794572</v>
       </c>
       <c r="B37" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,40 +4486,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481248</v>
+        <v>481322</v>
       </c>
       <c r="R37" t="n">
-        <v>6791582</v>
+        <v>6791606</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4547,14 +4543,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4563,19 +4564,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127794339</v>
+        <v>127794182</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>57833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4700,27 +4700,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4729,10 +4733,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481340</v>
+        <v>481374</v>
       </c>
       <c r="R39" t="n">
-        <v>6791650</v>
+        <v>6791645</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4801,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127794182</v>
+        <v>127794339</v>
       </c>
       <c r="B40" t="n">
-        <v>57832</v>
+        <v>57673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4812,31 +4816,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481374</v>
+        <v>481340</v>
       </c>
       <c r="R40" t="n">
-        <v>6791645</v>
+        <v>6791650</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -4920,7 +4920,7 @@
         <v>127802041</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>127795149</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>127795235</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>127802033</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>127802418</v>
       </c>
       <c r="B45" t="n">
-        <v>79618</v>
+        <v>79621</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5551,45 +5551,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127792736</v>
+        <v>127794070</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481195</v>
+        <v>481378</v>
       </c>
       <c r="R47" t="n">
-        <v>6791715</v>
+        <v>6791650</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5621,7 +5626,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5631,7 +5636,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5658,50 +5663,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127794070</v>
+        <v>127792736</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481378</v>
+        <v>481195</v>
       </c>
       <c r="R48" t="n">
-        <v>6791650</v>
+        <v>6791715</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127802578</v>
+        <v>127801956</v>
       </c>
       <c r="B49" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5781,21 +5781,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5804,14 +5804,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481315</v>
+        <v>481214</v>
       </c>
       <c r="R49" t="n">
-        <v>6791571</v>
+        <v>6791711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,11 +5846,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5864,22 +5859,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127801956</v>
+        <v>127802109</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5914,10 +5909,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481214</v>
+        <v>481301</v>
       </c>
       <c r="R50" t="n">
-        <v>6791711</v>
+        <v>6791736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5977,10 +5972,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127802109</v>
+        <v>127802578</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79064</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5988,21 +5983,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6011,14 +6006,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481301</v>
+        <v>481315</v>
       </c>
       <c r="R51" t="n">
-        <v>6791736</v>
+        <v>6791571</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6053,6 +6048,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6066,12 +6066,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6081,7 +6081,7 @@
         <v>127793494</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>127793626</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>127802018</v>
       </c>
       <c r="B54" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>127802564</v>
       </c>
       <c r="B55" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>127802064</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>127796163</v>
       </c>
       <c r="B57" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>127802522</v>
       </c>
       <c r="B58" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>127793176</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>127793847</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>127802028</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7138,51 +7138,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127801935</v>
+        <v>127793724</v>
       </c>
       <c r="B62" t="n">
-        <v>92642</v>
+        <v>57673</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481193</v>
+        <v>481344</v>
       </c>
       <c r="R62" t="n">
-        <v>6791714</v>
+        <v>6791702</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7209,18 +7211,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7232,60 +7243,58 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127793724</v>
+        <v>127801935</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481344</v>
+        <v>481193</v>
       </c>
       <c r="R63" t="n">
-        <v>6791702</v>
+        <v>6791714</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,27 +7321,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7354,7 +7354,7 @@
         <v>127794591</v>
       </c>
       <c r="B64" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>127801912</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>127802299</v>
       </c>
       <c r="B66" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>127802615</v>
       </c>
       <c r="B67" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>127837613</v>
       </c>
       <c r="B70" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>127836058</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -675,56 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127802601</v>
+        <v>127795277</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>56864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481305</v>
+        <v>481286</v>
       </c>
       <c r="R2" t="n">
-        <v>6791545</v>
+        <v>6791603</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,14 +762,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Stjärtfjäder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,79 +794,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127795277</v>
+        <v>127802601</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481286</v>
+        <v>481305</v>
       </c>
       <c r="R3" t="n">
-        <v>6791603</v>
+        <v>6791545</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,24 +882,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stjärtfjäder</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +904,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127801964</v>
+        <v>127795300</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,46 +1463,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481215</v>
+        <v>481286</v>
       </c>
       <c r="R9" t="n">
-        <v>6791716</v>
+        <v>6791603</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,18 +1520,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1552,45 +1552,45 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127794623</v>
+        <v>127794366</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481309</v>
+        <v>481336</v>
       </c>
       <c r="R10" t="n">
-        <v>6791590</v>
+        <v>6791622</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127795300</v>
+        <v>127794623</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1682,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481286</v>
+        <v>481309</v>
       </c>
       <c r="R11" t="n">
-        <v>6791603</v>
+        <v>6791590</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1741,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1756,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,53 +1783,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127794366</v>
+        <v>127801964</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481336</v>
+        <v>481215</v>
       </c>
       <c r="R12" t="n">
-        <v>6791622</v>
+        <v>6791716</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,27 +1860,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3082,50 +3082,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127793434</v>
+        <v>127794379</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481316</v>
+        <v>481338</v>
       </c>
       <c r="R24" t="n">
-        <v>6791716</v>
+        <v>6791608</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3157,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3167,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3194,53 +3189,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127795114</v>
+        <v>127802326</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481235</v>
+        <v>481261</v>
       </c>
       <c r="R25" t="n">
-        <v>6791533</v>
+        <v>6791722</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3267,19 +3260,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,69 +3276,72 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127802326</v>
+        <v>127793434</v>
       </c>
       <c r="B26" t="n">
-        <v>79064</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481261</v>
+        <v>481316</v>
       </c>
       <c r="R26" t="n">
-        <v>6791722</v>
+        <v>6791716</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3377,14 +3368,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,64 +3389,68 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127794379</v>
+        <v>127795114</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481338</v>
+        <v>481235</v>
       </c>
       <c r="R27" t="n">
-        <v>6791608</v>
+        <v>6791533</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5018,7 +5018,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127795149</v>
+        <v>127802033</v>
       </c>
       <c r="B42" t="n">
         <v>79032</v>
@@ -5047,19 +5047,22 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481247</v>
+        <v>481244</v>
       </c>
       <c r="R42" t="n">
-        <v>6791558</v>
+        <v>6791710</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5086,27 +5089,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5118,14 +5112,14 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127795235</v>
+        <v>127795149</v>
       </c>
       <c r="B43" t="n">
         <v>79032</v>
@@ -5160,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481286</v>
+        <v>481247</v>
       </c>
       <c r="R43" t="n">
-        <v>6791603</v>
+        <v>6791558</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5195,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5205,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127802033</v>
+        <v>127795235</v>
       </c>
       <c r="B44" t="n">
         <v>79032</v>
@@ -5261,22 +5255,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481244</v>
+        <v>481286</v>
       </c>
       <c r="R44" t="n">
-        <v>6791710</v>
+        <v>6791603</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5303,18 +5294,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5551,50 +5551,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127794070</v>
+        <v>127792736</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481378</v>
+        <v>481195</v>
       </c>
       <c r="R47" t="n">
-        <v>6791650</v>
+        <v>6791715</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5626,7 +5621,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5636,7 +5631,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5663,45 +5658,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127792736</v>
+        <v>127794070</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481195</v>
+        <v>481378</v>
       </c>
       <c r="R48" t="n">
-        <v>6791715</v>
+        <v>6791650</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6078,10 +6078,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127793494</v>
+        <v>127802018</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79064</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6089,37 +6089,40 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481328</v>
+        <v>481231</v>
       </c>
       <c r="R52" t="n">
-        <v>6791735</v>
+        <v>6791714</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6146,27 +6149,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6178,17 +6172,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127793626</v>
+        <v>127793494</v>
       </c>
       <c r="B53" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6196,39 +6190,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481354</v>
+        <v>481328</v>
       </c>
       <c r="R53" t="n">
-        <v>6791713</v>
+        <v>6791735</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6297,10 +6286,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127802018</v>
+        <v>127793626</v>
       </c>
       <c r="B54" t="n">
-        <v>79064</v>
+        <v>57673</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6308,40 +6297,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481231</v>
+        <v>481354</v>
       </c>
       <c r="R54" t="n">
-        <v>6791714</v>
+        <v>6791713</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6368,18 +6359,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127802522</v>
+        <v>127793176</v>
       </c>
       <c r="B58" t="n">
-        <v>79064</v>
+        <v>79032</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6728,40 +6728,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481351</v>
+        <v>481316</v>
       </c>
       <c r="R58" t="n">
-        <v>6791706</v>
+        <v>6791716</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6788,14 +6785,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6804,29 +6806,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127793176</v>
+        <v>127802522</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>79064</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6834,37 +6835,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481316</v>
+        <v>481351</v>
       </c>
       <c r="R59" t="n">
-        <v>6791716</v>
+        <v>6791706</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6891,19 +6895,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:04</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,18 +6911,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127795277</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -809,7 +809,7 @@
         <v>127802601</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802239</v>
+        <v>127802106</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,14 +950,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481187</v>
+        <v>481280</v>
       </c>
       <c r="R4" t="n">
-        <v>6791714</v>
+        <v>6791734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,11 +992,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en brändstubbe</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,22 +1005,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127794033</v>
+        <v>127802487</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,46 +1028,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481385</v>
+        <v>481325</v>
       </c>
       <c r="R5" t="n">
-        <v>6791690</v>
+        <v>6791701</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,19 +1088,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,18 +1104,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1141,7 +1126,7 @@
         <v>127794232</v>
       </c>
       <c r="B6" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127802106</v>
+        <v>127794033</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,40 +1241,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481280</v>
+        <v>481385</v>
       </c>
       <c r="R7" t="n">
-        <v>6791734</v>
+        <v>6791690</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,18 +1307,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127802487</v>
+        <v>127802239</v>
       </c>
       <c r="B8" t="n">
-        <v>79064</v>
+        <v>78841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481325</v>
+        <v>481187</v>
       </c>
       <c r="R8" t="n">
-        <v>6791701</v>
+        <v>6791714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en brändstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,45 +1452,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127795300</v>
+        <v>127794366</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481286</v>
+        <v>481336</v>
       </c>
       <c r="R9" t="n">
-        <v>6791603</v>
+        <v>6791622</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,50 +1564,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127794366</v>
+        <v>127795300</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481336</v>
+        <v>481286</v>
       </c>
       <c r="R10" t="n">
-        <v>6791622</v>
+        <v>6791603</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,14 +1664,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794623</v>
+        <v>127801964</v>
       </c>
       <c r="B11" t="n">
         <v>8450</v>
@@ -1700,24 +1700,28 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481309</v>
+        <v>481215</v>
       </c>
       <c r="R11" t="n">
-        <v>6791590</v>
+        <v>6791716</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,27 +1748,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,14 +1771,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127801964</v>
+        <v>127794623</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1812,28 +1807,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481215</v>
+        <v>481309</v>
       </c>
       <c r="R12" t="n">
-        <v>6791716</v>
+        <v>6791590</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,18 +1851,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127793859</v>
+        <v>127802005</v>
       </c>
       <c r="B13" t="n">
-        <v>79064</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,37 +1901,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481377</v>
+        <v>481219</v>
       </c>
       <c r="R13" t="n">
-        <v>6791659</v>
+        <v>6791708</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,27 +1961,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1990,17 +1984,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127802005</v>
+        <v>127794298</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,22 +2020,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481219</v>
+        <v>481340</v>
       </c>
       <c r="R14" t="n">
-        <v>6791708</v>
+        <v>6791650</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,18 +2059,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2091,17 +2091,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127801929</v>
+        <v>127793859</v>
       </c>
       <c r="B15" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,22 +2127,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481193</v>
+        <v>481377</v>
       </c>
       <c r="R15" t="n">
-        <v>6791718</v>
+        <v>6791659</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,18 +2166,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2192,17 +2198,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127802539</v>
+        <v>127802463</v>
       </c>
       <c r="B16" t="n">
-        <v>79064</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,37 +2216,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481318</v>
+        <v>481355</v>
       </c>
       <c r="R16" t="n">
-        <v>6791660</v>
+        <v>6791722</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2288,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,7 +2297,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2305,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127802463</v>
+        <v>127801929</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>79115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,42 +2326,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481355</v>
+        <v>481193</v>
       </c>
       <c r="R17" t="n">
-        <v>6791722</v>
+        <v>6791718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,82 +2391,76 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken i gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127794426</v>
+        <v>127802539</v>
       </c>
       <c r="B18" t="n">
-        <v>56864</v>
+        <v>79115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>481318</v>
       </c>
       <c r="R18" t="n">
-        <v>6791597</v>
+        <v>6791660</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2488,24 +2487,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,56 +2503,57 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127793635</v>
+        <v>127794426</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>56876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2572,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481357</v>
+        <v>481318</v>
       </c>
       <c r="R19" t="n">
-        <v>6791712</v>
+        <v>6791597</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2607,7 +2597,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2617,7 +2607,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,38 +2639,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127795085</v>
+        <v>127793635</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2684,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481240</v>
+        <v>481357</v>
       </c>
       <c r="R20" t="n">
-        <v>6791516</v>
+        <v>6791712</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2719,7 +2714,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2729,7 +2724,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,45 +2751,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127794298</v>
+        <v>127795085</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481340</v>
+        <v>481240</v>
       </c>
       <c r="R21" t="n">
-        <v>6791650</v>
+        <v>6791516</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,50 +2863,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127794064</v>
+        <v>127793514</v>
       </c>
       <c r="B22" t="n">
-        <v>57670</v>
+        <v>91417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481385</v>
+        <v>481353</v>
       </c>
       <c r="R22" t="n">
-        <v>6791690</v>
+        <v>6791723</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2975,45 +2970,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127793514</v>
+        <v>127794064</v>
       </c>
       <c r="B23" t="n">
-        <v>91325</v>
+        <v>57682</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481353</v>
+        <v>481385</v>
       </c>
       <c r="R23" t="n">
-        <v>6791723</v>
+        <v>6791690</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127794379</v>
+        <v>127802326</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,37 +3093,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481338</v>
+        <v>481261</v>
       </c>
       <c r="R24" t="n">
-        <v>6791608</v>
+        <v>6791722</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3150,19 +3153,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3171,28 +3169,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127802326</v>
+        <v>127794379</v>
       </c>
       <c r="B25" t="n">
-        <v>79064</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,40 +3199,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481261</v>
+        <v>481338</v>
       </c>
       <c r="R25" t="n">
-        <v>6791722</v>
+        <v>6791608</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3260,14 +3256,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,19 +3277,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3519,53 +3519,51 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127794470</v>
+        <v>127801926</v>
       </c>
       <c r="B28" t="n">
-        <v>56864</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481322</v>
+        <v>481193</v>
       </c>
       <c r="R28" t="n">
-        <v>6791606</v>
+        <v>6791718</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3592,32 +3590,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3629,60 +3613,58 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127794518</v>
+        <v>127802054</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481322</v>
+        <v>481267</v>
       </c>
       <c r="R29" t="n">
-        <v>6791606</v>
+        <v>6791723</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3709,27 +3691,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3741,58 +3714,60 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127801926</v>
+        <v>127794470</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>56876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R30" t="n">
-        <v>6791718</v>
+        <v>6791606</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3819,18 +3794,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3842,58 +3831,60 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127802054</v>
+        <v>127794518</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481267</v>
+        <v>481322</v>
       </c>
       <c r="R31" t="n">
-        <v>6791723</v>
+        <v>6791606</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3920,18 +3911,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3953,7 +3953,7 @@
         <v>127801947</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>127802179</v>
       </c>
       <c r="B33" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>127802625</v>
       </c>
       <c r="B34" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>127802354</v>
       </c>
       <c r="B35" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127802650</v>
       </c>
       <c r="B36" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>127794572</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4582,57 +4582,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127802504</v>
+        <v>127794339</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481325</v>
+        <v>481340</v>
       </c>
       <c r="R38" t="n">
-        <v>6791701</v>
+        <v>6791650</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4659,40 +4655,49 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127794182</v>
+        <v>127802041</v>
       </c>
       <c r="B39" t="n">
-        <v>57833</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4700,46 +4705,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481374</v>
+        <v>481251</v>
       </c>
       <c r="R39" t="n">
-        <v>6791645</v>
+        <v>6791716</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4766,27 +4765,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4798,60 +4788,64 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127794339</v>
+        <v>127802504</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481340</v>
+        <v>481325</v>
       </c>
       <c r="R40" t="n">
-        <v>6791650</v>
+        <v>6791701</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4878,49 +4872,40 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127802041</v>
+        <v>127794182</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>57845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4928,40 +4913,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481251</v>
+        <v>481374</v>
       </c>
       <c r="R41" t="n">
-        <v>6791716</v>
+        <v>6791645</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4988,18 +4979,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5011,17 +5011,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127802033</v>
+        <v>127795149</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5047,22 +5047,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481244</v>
+        <v>481247</v>
       </c>
       <c r="R42" t="n">
-        <v>6791710</v>
+        <v>6791558</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5089,18 +5086,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5112,17 +5118,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127795149</v>
+        <v>127795235</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5154,10 +5160,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481247</v>
+        <v>481286</v>
       </c>
       <c r="R43" t="n">
-        <v>6791558</v>
+        <v>6791603</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5189,7 +5195,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5205,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127795235</v>
+        <v>127802033</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5255,19 +5261,22 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481286</v>
+        <v>481244</v>
       </c>
       <c r="R44" t="n">
-        <v>6791603</v>
+        <v>6791710</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5294,27 +5303,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5336,7 +5336,7 @@
         <v>127802418</v>
       </c>
       <c r="B45" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5551,45 +5551,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127792736</v>
+        <v>127794070</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481195</v>
+        <v>481378</v>
       </c>
       <c r="R47" t="n">
-        <v>6791715</v>
+        <v>6791650</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5621,7 +5626,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5631,7 +5636,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5658,53 +5663,51 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127794070</v>
+        <v>127801956</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481378</v>
+        <v>481214</v>
       </c>
       <c r="R48" t="n">
-        <v>6791650</v>
+        <v>6791711</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5731,27 +5734,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5763,17 +5757,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127801956</v>
+        <v>127802109</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5808,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481214</v>
+        <v>481301</v>
       </c>
       <c r="R49" t="n">
-        <v>6791711</v>
+        <v>6791736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5871,10 +5865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127802109</v>
+        <v>127802578</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>79115</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,21 +5876,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5905,14 +5899,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481301</v>
+        <v>481315</v>
       </c>
       <c r="R50" t="n">
-        <v>6791736</v>
+        <v>6791571</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5947,6 +5941,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5960,22 +5959,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127802578</v>
+        <v>127792736</v>
       </c>
       <c r="B51" t="n">
-        <v>79064</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5983,40 +5982,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481315</v>
+        <v>481195</v>
       </c>
       <c r="R51" t="n">
-        <v>6791571</v>
+        <v>6791715</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6043,14 +6039,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6059,19 +6060,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6081,7 +6081,7 @@
         <v>127802018</v>
       </c>
       <c r="B52" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>127793494</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>127793626</v>
       </c>
       <c r="B54" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127802564</v>
+        <v>127802064</v>
       </c>
       <c r="B55" t="n">
-        <v>79064</v>
+        <v>79083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,21 +6409,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6432,14 +6432,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481366</v>
+        <v>481273</v>
       </c>
       <c r="R55" t="n">
-        <v>6791657</v>
+        <v>6791736</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,11 +6474,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6492,22 +6487,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802064</v>
+        <v>127802564</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>79115</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6515,21 +6510,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6538,14 +6533,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481273</v>
+        <v>481366</v>
       </c>
       <c r="R56" t="n">
-        <v>6791736</v>
+        <v>6791657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6580,6 +6575,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6593,12 +6593,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
         <v>127796163</v>
       </c>
       <c r="B57" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,17 +6710,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127793176</v>
+        <v>127802522</v>
       </c>
       <c r="B58" t="n">
-        <v>79032</v>
+        <v>79115</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6728,37 +6728,40 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481316</v>
+        <v>481351</v>
       </c>
       <c r="R58" t="n">
-        <v>6791716</v>
+        <v>6791706</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6785,19 +6788,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:04</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6806,28 +6804,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127802522</v>
+        <v>127793176</v>
       </c>
       <c r="B59" t="n">
-        <v>79064</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6835,40 +6834,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481351</v>
+        <v>481316</v>
       </c>
       <c r="R59" t="n">
-        <v>6791706</v>
+        <v>6791716</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6895,14 +6891,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6911,19 +6912,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6933,7 +6933,7 @@
         <v>127793847</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>127802028</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7138,53 +7138,51 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127793724</v>
+        <v>127801935</v>
       </c>
       <c r="B62" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481344</v>
+        <v>481193</v>
       </c>
       <c r="R62" t="n">
-        <v>6791702</v>
+        <v>6791714</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7211,27 +7209,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7243,58 +7232,55 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127801935</v>
+        <v>127794591</v>
       </c>
       <c r="B63" t="n">
-        <v>92650</v>
+        <v>79115</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R63" t="n">
-        <v>6791714</v>
+        <v>6791606</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7321,18 +7307,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7344,17 +7339,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127794591</v>
+        <v>127793724</v>
       </c>
       <c r="B64" t="n">
-        <v>79064</v>
+        <v>57685</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,34 +7357,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481322</v>
+        <v>481344</v>
       </c>
       <c r="R64" t="n">
-        <v>6791606</v>
+        <v>6791702</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7461,7 +7461,7 @@
         <v>127801912</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>127802299</v>
       </c>
       <c r="B66" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>127802615</v>
       </c>
       <c r="B67" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>127794665</v>
       </c>
       <c r="B68" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>127835551</v>
       </c>
       <c r="B69" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>127837613</v>
       </c>
       <c r="B70" t="n">
-        <v>58108</v>
+        <v>58120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>127836058</v>
       </c>
       <c r="B71" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>127837582</v>
       </c>
       <c r="B72" t="n">
-        <v>57558</v>
+        <v>57570</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -675,67 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127795277</v>
+        <v>127802601</v>
       </c>
       <c r="B2" t="n">
-        <v>56876</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481286</v>
+        <v>481305</v>
       </c>
       <c r="R2" t="n">
-        <v>6791603</v>
+        <v>6791545</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,24 +751,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stjärtfjäder</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,68 +773,79 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127802601</v>
+        <v>127795277</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>56876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481305</v>
+        <v>481286</v>
       </c>
       <c r="R3" t="n">
-        <v>6791545</v>
+        <v>6791603</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,14 +872,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Stjärtfjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802106</v>
+        <v>127802487</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,14 +950,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481280</v>
+        <v>481325</v>
       </c>
       <c r="R4" t="n">
-        <v>6791734</v>
+        <v>6791701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +992,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127802487</v>
+        <v>127802106</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481325</v>
+        <v>481280</v>
       </c>
       <c r="R5" t="n">
-        <v>6791701</v>
+        <v>6791734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,11 +1098,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127794232</v>
+        <v>127802239</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,37 +1134,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481340</v>
+        <v>481187</v>
       </c>
       <c r="R6" t="n">
-        <v>6791650</v>
+        <v>6791714</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,19 +1194,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en brändstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,28 +1210,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127794033</v>
+        <v>127794232</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,43 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481385</v>
+        <v>481340</v>
       </c>
       <c r="R7" t="n">
-        <v>6791690</v>
+        <v>6791650</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1309,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127802239</v>
+        <v>127794033</v>
       </c>
       <c r="B8" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,40 +1347,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481187</v>
+        <v>481385</v>
       </c>
       <c r="R8" t="n">
-        <v>6791714</v>
+        <v>6791690</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,14 +1413,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en brändstubbe</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,69 +1434,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127794366</v>
+        <v>127795300</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481336</v>
+        <v>481286</v>
       </c>
       <c r="R9" t="n">
-        <v>6791622</v>
+        <v>6791603</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,45 +1559,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127795300</v>
+        <v>127794366</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481286</v>
+        <v>481336</v>
       </c>
       <c r="R10" t="n">
-        <v>6791603</v>
+        <v>6791622</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,7 +1671,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127801964</v>
+        <v>127794623</v>
       </c>
       <c r="B11" t="n">
         <v>8450</v>
@@ -1700,28 +1700,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481215</v>
+        <v>481309</v>
       </c>
       <c r="R11" t="n">
-        <v>6791716</v>
+        <v>6791590</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,18 +1744,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1771,14 +1776,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127794623</v>
+        <v>127801964</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1807,24 +1812,28 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481309</v>
+        <v>481215</v>
       </c>
       <c r="R12" t="n">
-        <v>6791590</v>
+        <v>6791716</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,27 +1860,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,58 +1883,60 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127802005</v>
+        <v>127794426</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>56876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481219</v>
+        <v>481318</v>
       </c>
       <c r="R13" t="n">
-        <v>6791708</v>
+        <v>6791597</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,18 +1963,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,17 +2000,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127794298</v>
+        <v>127793635</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,34 +2018,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481340</v>
+        <v>481357</v>
       </c>
       <c r="R14" t="n">
-        <v>6791650</v>
+        <v>6791712</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2061,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2071,7 +2092,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,52 +2112,57 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127793859</v>
+        <v>127795085</v>
       </c>
       <c r="B15" t="n">
-        <v>79115</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481377</v>
+        <v>481240</v>
       </c>
       <c r="R15" t="n">
-        <v>6791659</v>
+        <v>6791516</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2168,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2178,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127802463</v>
+        <v>127794298</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,45 +2242,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481355</v>
+        <v>481340</v>
       </c>
       <c r="R16" t="n">
-        <v>6791722</v>
+        <v>6791650</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,14 +2299,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken i gran</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,12 +2326,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2522,53 +2545,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127794426</v>
+        <v>127802005</v>
       </c>
       <c r="B19" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481318</v>
+        <v>481219</v>
       </c>
       <c r="R19" t="n">
-        <v>6791597</v>
+        <v>6791708</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2595,32 +2616,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2632,14 +2639,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127793635</v>
+        <v>127802463</v>
       </c>
       <c r="B20" t="n">
         <v>57685</v>
@@ -2668,24 +2675,27 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481357</v>
+        <v>481355</v>
       </c>
       <c r="R20" t="n">
-        <v>6791712</v>
+        <v>6791722</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2712,19 +2722,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,62 +2744,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127795085</v>
+        <v>127793859</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79115</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481240</v>
+        <v>481377</v>
       </c>
       <c r="R21" t="n">
-        <v>6791516</v>
+        <v>6791659</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127802326</v>
+        <v>127794379</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,40 +3093,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481261</v>
+        <v>481338</v>
       </c>
       <c r="R24" t="n">
-        <v>6791722</v>
+        <v>6791608</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3153,14 +3150,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,29 +3171,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127794379</v>
+        <v>127802326</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,37 +3200,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481338</v>
+        <v>481261</v>
       </c>
       <c r="R25" t="n">
-        <v>6791608</v>
+        <v>6791722</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3256,19 +3260,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,18 +3276,19 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3943,17 +3943,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127801947</v>
+        <v>127802179</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,21 +3961,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,14 +3984,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481204</v>
+        <v>481186</v>
       </c>
       <c r="R32" t="n">
-        <v>6791711</v>
+        <v>6791726</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4026,6 +4026,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4039,22 +4044,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127802179</v>
+        <v>127801947</v>
       </c>
       <c r="B33" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4062,21 +4067,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,14 +4090,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481186</v>
+        <v>481204</v>
       </c>
       <c r="R33" t="n">
-        <v>6791726</v>
+        <v>6791711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,11 +4132,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4145,22 +4145,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127802625</v>
+        <v>127794572</v>
       </c>
       <c r="B34" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,40 +4168,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481275</v>
+        <v>481322</v>
       </c>
       <c r="R34" t="n">
-        <v>6791557</v>
+        <v>6791606</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,14 +4225,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,26 +4246,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802354</v>
+        <v>127802625</v>
       </c>
       <c r="B35" t="n">
         <v>79115</v>
@@ -4301,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481294</v>
+        <v>481275</v>
       </c>
       <c r="R35" t="n">
-        <v>6791733</v>
+        <v>6791557</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4369,7 +4370,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127802650</v>
+        <v>127802354</v>
       </c>
       <c r="B36" t="n">
         <v>79115</v>
@@ -4407,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481248</v>
+        <v>481294</v>
       </c>
       <c r="R36" t="n">
-        <v>6791582</v>
+        <v>6791733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4475,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127794572</v>
+        <v>127802650</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,37 +4487,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481322</v>
+        <v>481248</v>
       </c>
       <c r="R37" t="n">
-        <v>6791606</v>
+        <v>6791582</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4543,19 +4547,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4564,18 +4563,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4687,17 +4687,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127802041</v>
+        <v>127794182</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>57845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,40 +4705,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481251</v>
+        <v>481374</v>
       </c>
       <c r="R39" t="n">
-        <v>6791716</v>
+        <v>6791645</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4765,18 +4771,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4788,61 +4803,55 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127802504</v>
+        <v>127802041</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481325</v>
+        <v>481251</v>
       </c>
       <c r="R40" t="n">
-        <v>6791701</v>
+        <v>6791716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4890,69 +4899,69 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127794182</v>
+        <v>127802504</v>
       </c>
       <c r="B41" t="n">
-        <v>57845</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481374</v>
+        <v>481325</v>
       </c>
       <c r="R41" t="n">
-        <v>6791645</v>
+        <v>6791701</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4979,39 +4988,30 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127801956</v>
+        <v>127802578</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5674,21 +5674,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5697,14 +5697,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481214</v>
+        <v>481315</v>
       </c>
       <c r="R48" t="n">
-        <v>6791711</v>
+        <v>6791571</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5739,6 +5739,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5752,19 +5757,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127802109</v>
+        <v>127801956</v>
       </c>
       <c r="B49" t="n">
         <v>79083</v>
@@ -5802,10 +5807,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481301</v>
+        <v>481214</v>
       </c>
       <c r="R49" t="n">
-        <v>6791736</v>
+        <v>6791711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5865,10 +5870,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127802578</v>
+        <v>127802109</v>
       </c>
       <c r="B50" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5876,21 +5881,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5899,14 +5904,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481315</v>
+        <v>481301</v>
       </c>
       <c r="R50" t="n">
-        <v>6791571</v>
+        <v>6791736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,11 +5946,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5959,12 +5959,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127802018</v>
+        <v>127793494</v>
       </c>
       <c r="B52" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6089,40 +6089,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481231</v>
+        <v>481328</v>
       </c>
       <c r="R52" t="n">
-        <v>6791714</v>
+        <v>6791735</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6149,18 +6146,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6172,17 +6178,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127793494</v>
+        <v>127793626</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6190,34 +6196,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481328</v>
+        <v>481354</v>
       </c>
       <c r="R53" t="n">
-        <v>6791735</v>
+        <v>6791713</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6286,10 +6297,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127793626</v>
+        <v>127802018</v>
       </c>
       <c r="B54" t="n">
-        <v>57685</v>
+        <v>79115</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6297,42 +6308,40 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481354</v>
+        <v>481231</v>
       </c>
       <c r="R54" t="n">
-        <v>6791713</v>
+        <v>6791714</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6359,27 +6368,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6391,17 +6391,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127802064</v>
+        <v>127796163</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>57845</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,40 +6409,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481273</v>
+        <v>481305</v>
       </c>
       <c r="R55" t="n">
-        <v>6791736</v>
+        <v>6791432</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6469,18 +6471,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6492,17 +6503,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802564</v>
+        <v>127802064</v>
       </c>
       <c r="B56" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6510,21 +6521,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6533,14 +6544,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481366</v>
+        <v>481273</v>
       </c>
       <c r="R56" t="n">
-        <v>6791657</v>
+        <v>6791736</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6575,11 +6586,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6593,22 +6599,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127796163</v>
+        <v>127802564</v>
       </c>
       <c r="B57" t="n">
-        <v>57845</v>
+        <v>79115</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6616,42 +6622,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481305</v>
+        <v>481366</v>
       </c>
       <c r="R57" t="n">
-        <v>6791432</v>
+        <v>6791657</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6678,19 +6682,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6699,18 +6698,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7451,17 +7451,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127801912</v>
+        <v>127802299</v>
       </c>
       <c r="B65" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,14 +7492,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481175</v>
+        <v>481213</v>
       </c>
       <c r="R65" t="n">
-        <v>6791725</v>
+        <v>6791709</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,6 +7534,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7547,19 +7552,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127802299</v>
+        <v>127802615</v>
       </c>
       <c r="B66" t="n">
         <v>79115</v>
@@ -7597,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481213</v>
+        <v>481276</v>
       </c>
       <c r="R66" t="n">
-        <v>6791709</v>
+        <v>6791608</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7665,10 +7670,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127802615</v>
+        <v>127801912</v>
       </c>
       <c r="B67" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7676,21 +7681,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7699,14 +7704,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481276</v>
+        <v>481175</v>
       </c>
       <c r="R67" t="n">
-        <v>6791608</v>
+        <v>6791725</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,11 +7746,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,12 +7759,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -675,56 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127802601</v>
+        <v>127795277</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>56876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481305</v>
+        <v>481286</v>
       </c>
       <c r="R2" t="n">
-        <v>6791545</v>
+        <v>6791603</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,14 +762,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Stjärtfjäder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,79 +794,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127795277</v>
+        <v>127802601</v>
       </c>
       <c r="B3" t="n">
-        <v>56876</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481286</v>
+        <v>481305</v>
       </c>
       <c r="R3" t="n">
-        <v>6791603</v>
+        <v>6791545</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,24 +882,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stjärtfjäder</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,19 +904,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127802487</v>
+        <v>127794232</v>
       </c>
       <c r="B4" t="n">
         <v>79115</v>
@@ -945,22 +945,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481325</v>
+        <v>481340</v>
       </c>
       <c r="R4" t="n">
-        <v>6791701</v>
+        <v>6791650</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,14 +984,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,29 +1005,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127802106</v>
+        <v>127794033</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,40 +1034,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481280</v>
+        <v>481385</v>
       </c>
       <c r="R5" t="n">
-        <v>6791734</v>
+        <v>6791690</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,18 +1100,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,7 +1132,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1229,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127794232</v>
+        <v>127802487</v>
       </c>
       <c r="B7" t="n">
         <v>79115</v>
@@ -1258,19 +1274,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481340</v>
+        <v>481325</v>
       </c>
       <c r="R7" t="n">
-        <v>6791650</v>
+        <v>6791701</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,19 +1316,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,28 +1332,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127794033</v>
+        <v>127802106</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,46 +1362,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481385</v>
+        <v>481280</v>
       </c>
       <c r="R8" t="n">
-        <v>6791690</v>
+        <v>6791734</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,27 +1422,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,17 +1445,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127795300</v>
+        <v>127794623</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1463,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481286</v>
+        <v>481309</v>
       </c>
       <c r="R9" t="n">
-        <v>6791603</v>
+        <v>6791590</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,50 +1564,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127794366</v>
+        <v>127795300</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481336</v>
+        <v>481286</v>
       </c>
       <c r="R10" t="n">
-        <v>6791622</v>
+        <v>6791603</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,45 +1664,45 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794623</v>
+        <v>127794366</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481309</v>
+        <v>481336</v>
       </c>
       <c r="R11" t="n">
-        <v>6791590</v>
+        <v>6791622</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1890,38 +1890,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127794426</v>
+        <v>127793635</v>
       </c>
       <c r="B13" t="n">
-        <v>56876</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481318</v>
+        <v>481357</v>
       </c>
       <c r="R13" t="n">
-        <v>6791597</v>
+        <v>6791712</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1975,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127793635</v>
+        <v>127793859</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>79115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,39 +2013,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481357</v>
+        <v>481377</v>
       </c>
       <c r="R14" t="n">
-        <v>6791712</v>
+        <v>6791659</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2112,57 +2102,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127795085</v>
+        <v>127794298</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481240</v>
+        <v>481340</v>
       </c>
       <c r="R15" t="n">
-        <v>6791516</v>
+        <v>6791650</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2194,7 +2179,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2189,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,45 +2216,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127794298</v>
+        <v>127794426</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>56876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481340</v>
+        <v>481318</v>
       </c>
       <c r="R16" t="n">
-        <v>6791650</v>
+        <v>6791597</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2301,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,7 +2301,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2756,45 +2751,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127793859</v>
+        <v>127795085</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481377</v>
+        <v>481240</v>
       </c>
       <c r="R21" t="n">
-        <v>6791659</v>
+        <v>6791516</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,45 +2863,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127793514</v>
+        <v>127794064</v>
       </c>
       <c r="B22" t="n">
-        <v>91417</v>
+        <v>57682</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481353</v>
+        <v>481385</v>
       </c>
       <c r="R22" t="n">
-        <v>6791723</v>
+        <v>6791690</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2970,50 +2975,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127794064</v>
+        <v>127793514</v>
       </c>
       <c r="B23" t="n">
-        <v>57682</v>
+        <v>91417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481385</v>
+        <v>481353</v>
       </c>
       <c r="R23" t="n">
-        <v>6791690</v>
+        <v>6791723</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127794379</v>
+        <v>127802326</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,37 +3093,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481338</v>
+        <v>481261</v>
       </c>
       <c r="R24" t="n">
-        <v>6791608</v>
+        <v>6791722</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3150,19 +3153,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3171,69 +3169,72 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127802326</v>
+        <v>127795114</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481261</v>
+        <v>481235</v>
       </c>
       <c r="R25" t="n">
-        <v>6791722</v>
+        <v>6791533</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3260,14 +3261,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,19 +3282,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3407,50 +3412,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127795114</v>
+        <v>127794379</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481235</v>
+        <v>481338</v>
       </c>
       <c r="R27" t="n">
-        <v>6791533</v>
+        <v>6791608</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,58 +3512,60 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127801926</v>
+        <v>127794518</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R28" t="n">
-        <v>6791718</v>
+        <v>6791606</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,18 +3592,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3613,58 +3624,60 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127802054</v>
+        <v>127794470</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>56876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481267</v>
+        <v>481322</v>
       </c>
       <c r="R29" t="n">
-        <v>6791723</v>
+        <v>6791606</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3691,18 +3704,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3714,60 +3741,58 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127794470</v>
+        <v>127801926</v>
       </c>
       <c r="B30" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481322</v>
+        <v>481193</v>
       </c>
       <c r="R30" t="n">
-        <v>6791606</v>
+        <v>6791718</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3794,32 +3819,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3831,60 +3842,58 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127794518</v>
+        <v>127802054</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481322</v>
+        <v>481267</v>
       </c>
       <c r="R31" t="n">
-        <v>6791606</v>
+        <v>6791723</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3911,27 +3920,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3943,17 +3943,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127802179</v>
+        <v>127801947</v>
       </c>
       <c r="B32" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,21 +3961,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,14 +3984,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481186</v>
+        <v>481204</v>
       </c>
       <c r="R32" t="n">
-        <v>6791726</v>
+        <v>6791711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4026,11 +4026,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4044,22 +4039,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127801947</v>
+        <v>127802179</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4090,14 +4085,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481204</v>
+        <v>481186</v>
       </c>
       <c r="R33" t="n">
-        <v>6791711</v>
+        <v>6791726</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4132,6 +4127,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4145,12 +4145,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4582,53 +4582,57 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127794339</v>
+        <v>127802504</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481340</v>
+        <v>481325</v>
       </c>
       <c r="R38" t="n">
-        <v>6791650</v>
+        <v>6791701</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4655,49 +4659,40 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127794182</v>
+        <v>127802041</v>
       </c>
       <c r="B39" t="n">
-        <v>57845</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,46 +4700,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481374</v>
+        <v>481251</v>
       </c>
       <c r="R39" t="n">
-        <v>6791645</v>
+        <v>6791716</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4771,27 +4760,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4803,17 +4783,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127802041</v>
+        <v>127794182</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>57845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,40 +4801,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481251</v>
+        <v>481374</v>
       </c>
       <c r="R40" t="n">
-        <v>6791716</v>
+        <v>6791645</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4881,18 +4867,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4904,64 +4899,60 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127802504</v>
+        <v>127794339</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481325</v>
+        <v>481340</v>
       </c>
       <c r="R41" t="n">
-        <v>6791701</v>
+        <v>6791650</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4988,30 +4979,39 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127802578</v>
+        <v>127792736</v>
       </c>
       <c r="B48" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5674,40 +5674,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481315</v>
+        <v>481195</v>
       </c>
       <c r="R48" t="n">
-        <v>6791571</v>
+        <v>6791715</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5734,14 +5731,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5750,29 +5752,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127801956</v>
+        <v>127802578</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5780,21 +5781,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5803,14 +5804,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481214</v>
+        <v>481315</v>
       </c>
       <c r="R49" t="n">
-        <v>6791711</v>
+        <v>6791571</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5845,6 +5846,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5858,19 +5864,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127802109</v>
+        <v>127801956</v>
       </c>
       <c r="B50" t="n">
         <v>79083</v>
@@ -5908,10 +5914,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481301</v>
+        <v>481214</v>
       </c>
       <c r="R50" t="n">
-        <v>6791736</v>
+        <v>6791711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5971,7 +5977,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127792736</v>
+        <v>127802109</v>
       </c>
       <c r="B51" t="n">
         <v>79083</v>
@@ -6000,19 +6006,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481195</v>
+        <v>481301</v>
       </c>
       <c r="R51" t="n">
-        <v>6791715</v>
+        <v>6791736</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6039,27 +6048,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802064</v>
+        <v>127802564</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6544,14 +6544,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481273</v>
+        <v>481366</v>
       </c>
       <c r="R56" t="n">
-        <v>6791736</v>
+        <v>6791657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6586,6 +6586,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6599,22 +6604,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127802564</v>
+        <v>127802064</v>
       </c>
       <c r="B57" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6622,21 +6627,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6645,14 +6650,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481366</v>
+        <v>481273</v>
       </c>
       <c r="R57" t="n">
-        <v>6791657</v>
+        <v>6791736</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,11 +6692,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6705,22 +6705,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127802522</v>
+        <v>127793176</v>
       </c>
       <c r="B58" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6728,40 +6728,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481351</v>
+        <v>481316</v>
       </c>
       <c r="R58" t="n">
-        <v>6791706</v>
+        <v>6791716</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6788,14 +6785,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6804,29 +6806,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127793176</v>
+        <v>127802522</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6834,37 +6835,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481316</v>
+        <v>481351</v>
       </c>
       <c r="R59" t="n">
-        <v>6791716</v>
+        <v>6791706</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6891,19 +6895,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:04</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,18 +6911,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7138,51 +7138,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127801935</v>
+        <v>127793724</v>
       </c>
       <c r="B62" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481193</v>
+        <v>481344</v>
       </c>
       <c r="R62" t="n">
-        <v>6791714</v>
+        <v>6791702</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7209,18 +7211,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7232,7 +7243,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7346,53 +7357,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127793724</v>
+        <v>127801935</v>
       </c>
       <c r="B64" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481344</v>
+        <v>481193</v>
       </c>
       <c r="R64" t="n">
-        <v>6791702</v>
+        <v>6791714</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7419,27 +7428,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127795277</v>
+        <v>127793859</v>
       </c>
       <c r="B2" t="n">
-        <v>56876</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481286</v>
+        <v>481377</v>
       </c>
       <c r="R2" t="n">
-        <v>6791603</v>
+        <v>6791659</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -764,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127802601</v>
+        <v>127794232</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,45 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481305</v>
+        <v>481340</v>
       </c>
       <c r="R3" t="n">
-        <v>6791545</v>
+        <v>6791650</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,14 +850,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127794232</v>
+        <v>127794591</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481340</v>
+        <v>481322</v>
       </c>
       <c r="R4" t="n">
-        <v>6791650</v>
+        <v>6791606</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -986,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127794033</v>
+        <v>127801929</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,46 +1007,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481385</v>
+        <v>481193</v>
       </c>
       <c r="R5" t="n">
-        <v>6791690</v>
+        <v>6791718</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,27 +1067,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,17 +1090,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127802239</v>
+        <v>127802018</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,11 +1131,11 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481187</v>
+        <v>481231</v>
       </c>
       <c r="R6" t="n">
         <v>6791714</v>
@@ -1215,11 +1173,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en brändstubbe</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1233,22 +1186,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127802487</v>
+        <v>127802088</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,14 +1232,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481325</v>
+        <v>481279</v>
       </c>
       <c r="R7" t="n">
-        <v>6791701</v>
+        <v>6791743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,11 +1274,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1339,22 +1287,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127802106</v>
+        <v>127802179</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1385,14 +1333,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481280</v>
+        <v>481186</v>
       </c>
       <c r="R8" t="n">
-        <v>6791734</v>
+        <v>6791726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,6 +1375,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1440,65 +1393,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127794623</v>
+        <v>127802299</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481309</v>
+        <v>481213</v>
       </c>
       <c r="R9" t="n">
-        <v>6791590</v>
+        <v>6791709</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,19 +1476,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,66 +1492,70 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127795300</v>
+        <v>127802326</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481286</v>
+        <v>481261</v>
       </c>
       <c r="R10" t="n">
-        <v>6791603</v>
+        <v>6791722</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,19 +1582,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,28 +1598,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127794366</v>
+        <v>127802354</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,42 +1628,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481336</v>
+        <v>481294</v>
       </c>
       <c r="R11" t="n">
-        <v>6791622</v>
+        <v>6791733</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,19 +1688,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,72 +1704,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127801964</v>
+        <v>127802397</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481215</v>
+        <v>481340</v>
       </c>
       <c r="R12" t="n">
-        <v>6791716</v>
+        <v>6791744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,6 +1799,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1878,22 +1817,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127793635</v>
+        <v>127802487</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,42 +1840,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481357</v>
+        <v>481325</v>
       </c>
       <c r="R13" t="n">
-        <v>6791712</v>
+        <v>6791701</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,19 +1900,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,28 +1916,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127793859</v>
+        <v>127802522</v>
       </c>
       <c r="B14" t="n">
-        <v>79115</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,19 +1964,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481377</v>
+        <v>481351</v>
       </c>
       <c r="R14" t="n">
-        <v>6791659</v>
+        <v>6791706</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2070,19 +2006,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,28 +2022,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127794298</v>
+        <v>127802539</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,37 +2052,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481340</v>
+        <v>481318</v>
       </c>
       <c r="R15" t="n">
-        <v>6791650</v>
+        <v>6791660</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,19 +2112,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:56</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,71 +2128,70 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127794426</v>
+        <v>127802564</v>
       </c>
       <c r="B16" t="n">
-        <v>56876</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481318</v>
+        <v>481366</v>
       </c>
       <c r="R16" t="n">
-        <v>6791597</v>
+        <v>6791657</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,24 +2218,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,28 +2234,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127801929</v>
+        <v>127802578</v>
       </c>
       <c r="B17" t="n">
-        <v>79115</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,14 +2287,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481193</v>
+        <v>481315</v>
       </c>
       <c r="R17" t="n">
-        <v>6791718</v>
+        <v>6791571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,6 +2329,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2422,22 +2347,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127802539</v>
+        <v>127802615</v>
       </c>
       <c r="B18" t="n">
-        <v>79115</v>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481318</v>
+        <v>481276</v>
       </c>
       <c r="R18" t="n">
-        <v>6791660</v>
+        <v>6791608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,10 +2465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127802005</v>
+        <v>127802625</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,14 +2499,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481219</v>
+        <v>481275</v>
       </c>
       <c r="R19" t="n">
-        <v>6791708</v>
+        <v>6791557</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,6 +2541,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2629,22 +2559,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127802463</v>
+        <v>127802650</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,42 +2582,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedvassaln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481355</v>
+        <v>481248</v>
       </c>
       <c r="R20" t="n">
-        <v>6791722</v>
+        <v>6791582</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,7 +2649,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre hackmärken i gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2733,6 +2658,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2751,50 +2677,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127795085</v>
+        <v>127795300</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481240</v>
+        <v>481286</v>
       </c>
       <c r="R21" t="n">
-        <v>6791516</v>
+        <v>6791603</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2826,7 +2747,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2836,7 +2757,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,10 +2784,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127794064</v>
+        <v>127801935</v>
       </c>
       <c r="B22" t="n">
-        <v>57682</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,42 +2795,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481385</v>
+        <v>481193</v>
       </c>
       <c r="R22" t="n">
-        <v>6791690</v>
+        <v>6791714</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2936,27 +2855,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2968,7 +2878,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2978,7 +2888,7 @@
         <v>127793514</v>
       </c>
       <c r="B23" t="n">
-        <v>91417</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,51 +2992,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127802326</v>
+        <v>127792736</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481261</v>
+        <v>481195</v>
       </c>
       <c r="R24" t="n">
-        <v>6791722</v>
+        <v>6791715</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3153,14 +3060,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,69 +3081,63 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127795114</v>
+        <v>127793176</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481235</v>
+        <v>481316</v>
       </c>
       <c r="R25" t="n">
-        <v>6791533</v>
+        <v>6791716</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3263,7 +3169,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3179,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,50 +3206,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127793434</v>
+        <v>127793494</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481316</v>
+        <v>481328</v>
       </c>
       <c r="R26" t="n">
-        <v>6791716</v>
+        <v>6791735</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3375,7 +3276,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3286,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,14 +3313,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127794379</v>
+        <v>127793847</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3447,13 +3348,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481338</v>
+        <v>481358</v>
       </c>
       <c r="R27" t="n">
-        <v>6791608</v>
+        <v>6791667</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3482,7 +3383,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3492,7 +3393,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,57 +3413,52 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127794518</v>
+        <v>127794298</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481322</v>
+        <v>481340</v>
       </c>
       <c r="R28" t="n">
-        <v>6791606</v>
+        <v>6791650</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3594,7 +3490,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3604,7 +3500,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,50 +3527,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127794470</v>
+        <v>127794379</v>
       </c>
       <c r="B29" t="n">
-        <v>56876</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481322</v>
+        <v>481338</v>
       </c>
       <c r="R29" t="n">
-        <v>6791606</v>
+        <v>6791608</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3706,7 +3597,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3607,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Balgrop och fjäder fr tupp</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,21 +3627,21 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127801926</v>
+        <v>127794572</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3777,22 +3663,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481193</v>
+        <v>481322</v>
       </c>
       <c r="R30" t="n">
-        <v>6791718</v>
+        <v>6791606</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3819,18 +3702,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3842,21 +3734,21 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127802054</v>
+        <v>127795149</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3878,22 +3770,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481267</v>
+        <v>481247</v>
       </c>
       <c r="R31" t="n">
-        <v>6791723</v>
+        <v>6791558</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3920,18 +3809,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3943,21 +3841,21 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127801947</v>
+        <v>127795235</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3979,22 +3877,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481204</v>
+        <v>481286</v>
       </c>
       <c r="R32" t="n">
-        <v>6791711</v>
+        <v>6791603</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4021,18 +3916,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4044,39 +3948,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127802179</v>
+        <v>127801912</v>
       </c>
       <c r="B33" t="n">
-        <v>79115</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,14 +3989,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481186</v>
+        <v>481175</v>
       </c>
       <c r="R33" t="n">
-        <v>6791726</v>
+        <v>6791725</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,11 +4031,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4145,26 +4044,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127794572</v>
+        <v>127801926</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4186,19 +4085,22 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481322</v>
+        <v>481193</v>
       </c>
       <c r="R34" t="n">
-        <v>6791606</v>
+        <v>6791718</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4225,27 +4127,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4257,39 +4150,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127802625</v>
+        <v>127801947</v>
       </c>
       <c r="B35" t="n">
-        <v>79115</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4298,14 +4191,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481275</v>
+        <v>481204</v>
       </c>
       <c r="R35" t="n">
-        <v>6791557</v>
+        <v>6791711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4340,11 +4233,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4358,44 +4246,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127802354</v>
+        <v>127801956</v>
       </c>
       <c r="B36" t="n">
-        <v>79115</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4404,14 +4292,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481294</v>
+        <v>481214</v>
       </c>
       <c r="R36" t="n">
-        <v>6791733</v>
+        <v>6791711</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4446,11 +4334,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4464,44 +4347,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127802650</v>
+        <v>127802005</v>
       </c>
       <c r="B37" t="n">
-        <v>79115</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4510,14 +4393,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481248</v>
+        <v>481219</v>
       </c>
       <c r="R37" t="n">
-        <v>6791582</v>
+        <v>6791708</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4552,11 +4435,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4570,66 +4448,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127802504</v>
+        <v>127802028</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481325</v>
+        <v>481231</v>
       </c>
       <c r="R38" t="n">
-        <v>6791701</v>
+        <v>6791720</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,26 +4549,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127802041</v>
+        <v>127802033</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4727,10 +4599,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481251</v>
+        <v>481244</v>
       </c>
       <c r="R39" t="n">
-        <v>6791716</v>
+        <v>6791710</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,57 +4662,51 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127794182</v>
+        <v>127802041</v>
       </c>
       <c r="B40" t="n">
-        <v>57845</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481374</v>
+        <v>481251</v>
       </c>
       <c r="R40" t="n">
-        <v>6791645</v>
+        <v>6791716</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4867,27 +4733,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4899,60 +4756,58 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127794339</v>
+        <v>127802054</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481340</v>
+        <v>481267</v>
       </c>
       <c r="R41" t="n">
-        <v>6791650</v>
+        <v>6791723</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4979,27 +4834,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5011,21 +4857,21 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127795149</v>
+        <v>127802064</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5047,19 +4893,22 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481247</v>
+        <v>481273</v>
       </c>
       <c r="R42" t="n">
-        <v>6791558</v>
+        <v>6791736</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5086,27 +4935,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5118,21 +4958,21 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127795235</v>
+        <v>127802074</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5154,19 +4994,22 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481286</v>
+        <v>481280</v>
       </c>
       <c r="R43" t="n">
-        <v>6791603</v>
+        <v>6791747</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5193,27 +5036,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5225,21 +5059,21 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127802033</v>
+        <v>127802106</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5270,10 +5104,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481244</v>
+        <v>481280</v>
       </c>
       <c r="R44" t="n">
-        <v>6791710</v>
+        <v>6791734</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5333,32 +5167,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127802418</v>
+        <v>127802109</v>
       </c>
       <c r="B45" t="n">
-        <v>79673</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5367,14 +5201,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481333</v>
+        <v>481301</v>
       </c>
       <c r="R45" t="n">
-        <v>6791733</v>
+        <v>6791736</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5409,11 +5243,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5427,22 +5256,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127793574</v>
+        <v>127794064</v>
       </c>
       <c r="B46" t="n">
-        <v>5177</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,27 +5279,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5479,10 +5308,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481353</v>
+        <v>481385</v>
       </c>
       <c r="R46" t="n">
-        <v>6791723</v>
+        <v>6791690</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5551,53 +5380,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127794070</v>
+        <v>127837582</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>57838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481378</v>
+        <v>481203</v>
       </c>
       <c r="R47" t="n">
-        <v>6791650</v>
+        <v>6791678</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5621,22 +5454,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5656,17 +5489,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127792736</v>
+        <v>127793626</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5674,34 +5507,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481195</v>
+        <v>481354</v>
       </c>
       <c r="R48" t="n">
-        <v>6791715</v>
+        <v>6791713</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5733,7 +5571,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5743,7 +5581,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5770,10 +5608,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127802578</v>
+        <v>127793635</v>
       </c>
       <c r="B49" t="n">
-        <v>79115</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5781,40 +5619,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481315</v>
+        <v>481357</v>
       </c>
       <c r="R49" t="n">
-        <v>6791571</v>
+        <v>6791712</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5841,14 +5681,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5857,29 +5702,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127801956</v>
+        <v>127793724</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,40 +5731,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481214</v>
+        <v>481344</v>
       </c>
       <c r="R50" t="n">
-        <v>6791711</v>
+        <v>6791702</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5947,18 +5793,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5970,17 +5825,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127802109</v>
+        <v>127794033</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5988,40 +5843,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481301</v>
+        <v>481385</v>
       </c>
       <c r="R51" t="n">
-        <v>6791736</v>
+        <v>6791690</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6048,18 +5909,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6071,17 +5941,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127793494</v>
+        <v>127794339</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6089,34 +5959,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481328</v>
+        <v>481340</v>
       </c>
       <c r="R52" t="n">
-        <v>6791735</v>
+        <v>6791650</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6148,7 +6023,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6158,7 +6033,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6178,17 +6053,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127793626</v>
+        <v>127794366</v>
       </c>
       <c r="B53" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6216,7 +6091,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6225,10 +6100,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481354</v>
+        <v>481336</v>
       </c>
       <c r="R53" t="n">
-        <v>6791713</v>
+        <v>6791622</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6260,7 +6135,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6270,7 +6145,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6290,17 +6165,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127802018</v>
+        <v>127802463</v>
       </c>
       <c r="B54" t="n">
-        <v>79115</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6308,37 +6183,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481231</v>
+        <v>481355</v>
       </c>
       <c r="R54" t="n">
-        <v>6791714</v>
+        <v>6791722</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6373,35 +6253,39 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken i gran</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127796163</v>
+        <v>127802601</v>
       </c>
       <c r="B55" t="n">
-        <v>57845</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,42 +6293,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Hedvassaln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>481305</v>
       </c>
       <c r="R55" t="n">
-        <v>6791432</v>
+        <v>6791545</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6471,19 +6358,14 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6498,63 +6380,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127802564</v>
+        <v>127794426</v>
       </c>
       <c r="B56" t="n">
-        <v>79115</v>
+        <v>57141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481366</v>
+        <v>481318</v>
       </c>
       <c r="R56" t="n">
-        <v>6791657</v>
+        <v>6791597</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6581,14 +6465,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6597,70 +6491,71 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127802064</v>
+        <v>127794470</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481273</v>
+        <v>481322</v>
       </c>
       <c r="R57" t="n">
-        <v>6791736</v>
+        <v>6791606</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6687,18 +6582,32 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Balgrop och fjäder fr tupp</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6710,55 +6619,63 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127793176</v>
+        <v>127794665</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481316</v>
+        <v>481309</v>
       </c>
       <c r="R58" t="n">
-        <v>6791716</v>
+        <v>6791590</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6787,7 +6704,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6797,7 +6714,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ett par exemplar av spelspillning syns på stenen. Det som ytterligare talar för spel på denna plats är att stenen är sliten och avskavd på lavar och mossor. Stenen är belägen på en höjd nära en myr. Intill platsen med spelspillning hittades stjärtpenna av tupp, tuppdun vid balgrop samt även ytterligare en fjäder av tupp samt bajs. Sannolikt är det ett tjäderspel på båda sidor av myren, men detta behöver utredas ytterligare.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6824,51 +6746,67 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127802522</v>
+        <v>127795277</v>
       </c>
       <c r="B59" t="n">
-        <v>79115</v>
+        <v>57141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481351</v>
+        <v>481286</v>
       </c>
       <c r="R59" t="n">
-        <v>6791706</v>
+        <v>6791603</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6895,14 +6833,24 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Stjärtfjäder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6911,67 +6859,71 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127793847</v>
+        <v>127835551</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>57141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481358</v>
+        <v>481194</v>
       </c>
       <c r="R60" t="n">
-        <v>6791667</v>
+        <v>6791696</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6995,22 +6947,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7030,58 +6982,60 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127802028</v>
+        <v>127793574</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>5179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481231</v>
+        <v>481353</v>
       </c>
       <c r="R61" t="n">
-        <v>6791720</v>
+        <v>6791723</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7108,18 +7062,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7131,17 +7094,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127793724</v>
+        <v>127837613</v>
       </c>
       <c r="B62" t="n">
-        <v>57685</v>
+        <v>58393</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7149,42 +7112,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>102999</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hedvasslan, Hedvasslan, Dlr</t>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481344</v>
+        <v>481203</v>
       </c>
       <c r="R62" t="n">
-        <v>6791702</v>
+        <v>6791678</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7208,22 +7175,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7243,17 +7210,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127794591</v>
+        <v>127794182</v>
       </c>
       <c r="B63" t="n">
-        <v>79115</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7261,34 +7228,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481322</v>
+        <v>481374</v>
       </c>
       <c r="R63" t="n">
-        <v>6791606</v>
+        <v>6791645</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7320,7 +7296,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7330,7 +7306,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7357,51 +7333,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127801935</v>
+        <v>127796163</v>
       </c>
       <c r="B64" t="n">
-        <v>92742</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481193</v>
+        <v>481305</v>
       </c>
       <c r="R64" t="n">
-        <v>6791714</v>
+        <v>6791432</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7428,18 +7406,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7451,58 +7438,60 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127802299</v>
+        <v>127793434</v>
       </c>
       <c r="B65" t="n">
-        <v>79115</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481213</v>
+        <v>481316</v>
       </c>
       <c r="R65" t="n">
-        <v>6791709</v>
+        <v>6791716</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7529,14 +7518,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7545,70 +7539,71 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127802615</v>
+        <v>127794070</v>
       </c>
       <c r="B66" t="n">
-        <v>79115</v>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481276</v>
+        <v>481378</v>
       </c>
       <c r="R66" t="n">
-        <v>6791608</v>
+        <v>6791650</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7635,14 +7630,19 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7651,70 +7651,71 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127801912</v>
+        <v>127794518</v>
       </c>
       <c r="B67" t="n">
-        <v>79083</v>
+        <v>8455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481175</v>
+        <v>481322</v>
       </c>
       <c r="R67" t="n">
-        <v>6791725</v>
+        <v>6791606</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7741,18 +7742,27 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7764,17 +7774,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127794665</v>
+        <v>127794623</v>
       </c>
       <c r="B68" t="n">
-        <v>56876</v>
+        <v>8455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7782,32 +7792,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hedvasslan, Hedvasslan, Dlr</t>
@@ -7820,7 +7827,7 @@
         <v>6791590</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7849,7 +7856,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7859,12 +7866,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ett par exemplar av spelspillning syns på stenen. Det som ytterligare talar för spel på denna plats är att stenen är sliten och avskavd på lavar och mossor. Stenen är belägen på en höjd nära en myr. Intill platsen med spelspillning hittades stjärtpenna av tupp, tuppdun vid balgrop samt även ytterligare en fjäder av tupp samt bajs. Sannolikt är det ett tjäderspel på båda sidor av myren, men detta behöver utredas ytterligare.</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7891,10 +7893,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127835551</v>
+        <v>127795085</v>
       </c>
       <c r="B69" t="n">
-        <v>56876</v>
+        <v>8455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7902,39 +7904,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Svedvasslan, Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481194</v>
+        <v>481240</v>
       </c>
       <c r="R69" t="n">
-        <v>6791696</v>
+        <v>6791516</v>
       </c>
       <c r="S69" t="n">
         <v>9</v>
@@ -7961,22 +7963,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7996,64 +7998,60 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127837613</v>
+        <v>127795114</v>
       </c>
       <c r="B70" t="n">
-        <v>58120</v>
+        <v>8455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102999</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svedvasslan, Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481203</v>
+        <v>481235</v>
       </c>
       <c r="R70" t="n">
-        <v>6791678</v>
+        <v>6791533</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8077,22 +8075,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8112,55 +8110,64 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127836058</v>
+        <v>127801964</v>
       </c>
       <c r="B71" t="n">
-        <v>78841</v>
+        <v>8455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Svedvasslan, Svedvasslan, Dlr</t>
+          <t>Svedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481222</v>
+        <v>481215</v>
       </c>
       <c r="R71" t="n">
-        <v>6791673</v>
+        <v>6791716</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8184,22 +8191,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8208,6 +8205,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8226,10 +8224,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127837582</v>
+        <v>127802504</v>
       </c>
       <c r="B72" t="n">
-        <v>57570</v>
+        <v>8455</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8237,43 +8235,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100100</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svedvasslan, Svedvasslan, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481203</v>
+        <v>481325</v>
       </c>
       <c r="R72" t="n">
-        <v>6791678</v>
+        <v>6791701</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8300,22 +8298,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8324,21 +8312,341 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127802239</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>481187</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6791714</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På en brändstubbe</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127836058</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svedvasslan, Svedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>481222</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6791673</v>
+      </c>
+      <c r="S74" t="n">
+        <v>9</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
           <t>Bengt Oldhammer</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AX74" t="inlineStr">
         <is>
           <t>Bengt Oldhammer</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127802418</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hedvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>481333</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6791733</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38047-2025 artfynd.xlsx
+++ b/artfynd/A 38047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793859</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794232</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801929</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802018</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802088</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802326</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802354</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,6 +1881,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802397</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802487</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2038,6 +2103,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802522</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802539</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2250,6 +2325,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802564</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802578</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2462,6 +2547,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802615</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2568,6 +2658,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802625</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2674,6 +2769,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802650</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2781,6 +2881,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795300</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2882,6 +2987,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801935</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2989,6 +3099,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793514</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3096,6 +3211,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127792736</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3203,6 +3323,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793176</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3310,6 +3435,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793494</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3417,6 +3547,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793847</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3524,6 +3659,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794298</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3631,6 +3771,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794379</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3738,6 +3883,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794572</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3845,6 +3995,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795149</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3952,6 +4107,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795235</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4053,6 +4213,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801912</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4154,6 +4319,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801926</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4255,6 +4425,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801947</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4356,6 +4531,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801956</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4457,6 +4637,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802005</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4558,6 +4743,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802028</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4659,6 +4849,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802033</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4760,6 +4955,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802041</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4861,6 +5061,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802054</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4962,6 +5167,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802064</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5063,6 +5273,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802074</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5164,6 +5379,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802106</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5265,6 +5485,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802109</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5377,6 +5602,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794064</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5493,6 +5723,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837582</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5605,6 +5840,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793626</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5717,6 +5957,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793635</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5829,6 +6074,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793724</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5945,6 +6195,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794033</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6057,6 +6312,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794339</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6169,6 +6429,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794366</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6279,6 +6544,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802463</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6389,6 +6659,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802601</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6506,6 +6781,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794426</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6623,6 +6903,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794470</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6743,6 +7028,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794665</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6874,6 +7164,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795277</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6986,6 +7281,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127835551</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7098,6 +7398,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793574</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7214,6 +7519,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837613</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7330,6 +7640,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794182</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7442,6 +7757,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796163</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7554,6 +7874,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127793434</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7666,6 +7991,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794070</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7778,6 +8108,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794518</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7890,6 +8225,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794623</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8002,6 +8342,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795085</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8114,6 +8459,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795114</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8221,6 +8571,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801964</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8328,6 +8683,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802504</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8434,6 +8794,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802239</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8541,6 +8906,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836058</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8647,8 +9017,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802418</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>